--- a/marafiq_real_data.xlsx
+++ b/marafiq_real_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\azizs\Desktop\Last Standing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457A067C-062A-451A-846D-ADF7B661BD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D130EC10-FB09-44CA-85CB-24396EDEE92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="560">
   <si>
     <t>Contract Account</t>
   </si>
@@ -1484,9 +1484,6 @@
   </si>
   <si>
     <t>D5-01-013-119</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Fahad Abdullatif Buaiesha</t>
@@ -1709,9 +1706,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000000"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1784,28 +1778,185 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="51">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1936,188 +2087,28 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2136,18 +2127,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2A66777-ACB8-408F-8432-79F538ACC9A1}" name="Table1" displayName="Table1" ref="A1:L217" totalsRowShown="0">
   <autoFilter ref="A1:L217" xr:uid="{B2A66777-ACB8-408F-8432-79F538ACC9A1}"/>
   <tableColumns count="12">
-    <tableColumn id="3" xr3:uid="{44F335CF-8A5A-4524-8732-0F08F38C061D}" name="Account Determination"/>
-    <tableColumn id="4" xr3:uid="{FED333B4-4F7F-4275-BB56-93B1F5A5998B}" name="Meter Authenticated"/>
+    <tableColumn id="1" xr3:uid="{B2EF79CE-2355-4C95-8572-8FBD09E70056}" name="Contract Account" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{D790171C-F013-401A-BBB1-925EDD975462}" name="Name" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{44F335CF-8A5A-4524-8732-0F08F38C061D}" name="Account Determination" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{FED333B4-4F7F-4275-BB56-93B1F5A5998B}" name="Meter Authenticated" dataDxfId="47"/>
     <tableColumn id="5" xr3:uid="{9D975B51-1F15-4F1E-9C1B-9063F62C8935}" name="Tel No." dataDxfId="46"/>
-    <tableColumn id="1" xr3:uid="{B2EF79CE-2355-4C95-8572-8FBD09E70056}" name="Contract Account" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{D790171C-F013-401A-BBB1-925EDD975462}" name="Name" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{FF4D28BC-3CD3-40DF-A894-3696B92DA6F4}" name="Address"/>
-    <tableColumn id="7" xr3:uid="{AA4F0BD1-E9CC-4320-84AE-DD85C8D52B4D}" name="X"/>
-    <tableColumn id="8" xr3:uid="{8A857752-6004-4AB9-B561-B4D63C13211D}" name="Y"/>
+    <tableColumn id="6" xr3:uid="{FF4D28BC-3CD3-40DF-A894-3696B92DA6F4}" name="Address" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{AA4F0BD1-E9CC-4320-84AE-DD85C8D52B4D}" name="X" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{8A857752-6004-4AB9-B561-B4D63C13211D}" name="Y" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{C93F123E-73CA-485D-9E78-51652B475451}" name="Average Last 12 Months"/>
-    <tableColumn id="10" xr3:uid="{5E6A35A1-19A3-4B35-BE79-C988C55DA2E8}" name="Meter Status"/>
-    <tableColumn id="11" xr3:uid="{532CA3FA-D03C-4733-816A-CFF52DC7988A}" name="Zero Consumption"/>
-    <tableColumn id="12" xr3:uid="{A051709F-D764-47E5-BCFA-328F8B561282}" name="Disconnected and Consumption"/>
+    <tableColumn id="10" xr3:uid="{5E6A35A1-19A3-4B35-BE79-C988C55DA2E8}" name="Meter Status" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{532CA3FA-D03C-4733-816A-CFF52DC7988A}" name="Zero Consumption" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{A051709F-D764-47E5-BCFA-328F8B561282}" name="Disconnected and Consumption" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2445,9 +2436,9 @@
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.44140625" customWidth="1"/>
@@ -2456,27 +2447,27 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>184</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I1" t="s">
@@ -2493,28 +2484,28 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4">
+        <v>20089754</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2">
-        <v>20089754</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="9">
         <v>49.522150150000002</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="10">
         <v>27.184477999999999</v>
       </c>
       <c r="I2">
@@ -2531,28 +2522,28 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="5">
+        <v>20089755</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="6">
-        <v>20089755</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="11">
         <v>49.522334659999999</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="12">
         <v>27.184557330000001</v>
       </c>
       <c r="I3">
@@ -2569,28 +2560,28 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="6">
+        <v>20112631</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3">
-        <v>20112631</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="9">
         <v>49.522507330000003</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="10">
         <v>27.18462624</v>
       </c>
       <c r="I4">
@@ -2607,28 +2598,28 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="7">
+        <v>20089757</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7">
-        <v>20089757</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="11">
         <v>49.522687220000002</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="12">
         <v>27.184687830000001</v>
       </c>
       <c r="I5">
@@ -2645,28 +2636,28 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="6">
+        <v>20089758</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3">
-        <v>20089758</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="9">
         <v>49.522869329999999</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="10">
         <v>27.184741630000001</v>
       </c>
       <c r="I6">
@@ -2683,28 +2674,28 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="7">
+        <v>20114785</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="7">
-        <v>20114785</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <v>49.52306154</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="12">
         <v>27.184792529999999</v>
       </c>
       <c r="I7">
@@ -2721,28 +2712,28 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="6">
+        <v>20112656</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3">
-        <v>20112656</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="9">
         <v>49.523254379999997</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="10">
         <v>27.18483487</v>
       </c>
       <c r="I8">
@@ -2759,28 +2750,28 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="7">
+        <v>20109128</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7">
-        <v>20109128</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11">
         <v>49.523450699999998</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="12">
         <v>27.18487086</v>
       </c>
       <c r="I9">
@@ -2797,28 +2788,28 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="6">
+        <v>20112711</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3">
-        <v>20112711</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="9">
         <v>49.523769010000002</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="10">
         <v>27.184907760000002</v>
       </c>
       <c r="I10">
@@ -2835,28 +2826,28 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="7">
+        <v>20089489</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="7">
-        <v>20089489</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="11">
         <v>49.52395052</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="12">
         <v>27.184924890000001</v>
       </c>
       <c r="I11">
@@ -2873,28 +2864,28 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="4">
+        <v>20112716</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2">
-        <v>20112716</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="9">
         <v>49.524144479999997</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="10">
         <v>27.184929319999998</v>
       </c>
       <c r="I12">
@@ -2911,28 +2902,28 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="4">
+        <v>20068214</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="2">
-        <v>20068214</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="9">
         <v>49.54035932</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="10">
         <v>27.172168679999999</v>
       </c>
       <c r="I13">
@@ -2949,28 +2940,28 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="5">
+        <v>20068174</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="6">
-        <v>20068174</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="11">
         <v>49.540505119999999</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="12">
         <v>27.172266700000002</v>
       </c>
       <c r="I14">
@@ -2987,28 +2978,28 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="6">
+        <v>20068232</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="3">
-        <v>20068232</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="9">
         <v>49.540650309999997</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="10">
         <v>27.172364290000001</v>
       </c>
       <c r="I15">
@@ -3025,28 +3016,28 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="7">
+        <v>20068231</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="7">
-        <v>20068231</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="11">
         <v>49.540794980000001</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="12">
         <v>27.172461439999999</v>
       </c>
       <c r="I16">
@@ -3063,28 +3054,28 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="6">
+        <v>20097309</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="3">
-        <v>20097309</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="9">
         <v>49.540978930000001</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="10">
         <v>27.172610989999999</v>
       </c>
       <c r="I17">
@@ -3101,28 +3092,28 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="7">
+        <v>20100084</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="7">
-        <v>20100084</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="11">
         <v>49.54123981</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="12">
         <v>27.17264857</v>
       </c>
       <c r="I18">
@@ -3139,28 +3130,28 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="6">
+        <v>20147001</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="3">
-        <v>20147001</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="9">
         <v>49.541452390000003</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="10">
         <v>27.17247094</v>
       </c>
       <c r="I19">
@@ -3177,28 +3168,28 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="7">
+        <v>20121602</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="7">
-        <v>20121602</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="11">
         <v>49.541657720000003</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="12">
         <v>27.172336040000001</v>
       </c>
       <c r="I20">
@@ -3215,28 +3206,28 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="6">
+        <v>20100083</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="3">
-        <v>20100083</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="9">
         <v>49.541862739999999</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="10">
         <v>27.17220515</v>
       </c>
       <c r="I21">
@@ -3253,28 +3244,28 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="7">
+        <v>20068358</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="7">
-        <v>20068358</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="11">
         <v>49.542152090000002</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="12">
         <v>27.171992809999999</v>
       </c>
       <c r="I22">
@@ -3291,28 +3282,28 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="6">
+        <v>20068211</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="E23" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="3">
-        <v>20068211</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="9">
         <v>49.542360309999999</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="10">
         <v>27.171867169999999</v>
       </c>
       <c r="I23">
@@ -3329,28 +3320,28 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="4">
+        <v>20127788</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" t="s">
         <v>11</v>
       </c>
-      <c r="B24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="2">
-        <v>20127788</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="9">
         <v>49.522264389999997</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="10">
         <v>27.176176860000002</v>
       </c>
       <c r="I24">
@@ -3367,28 +3358,28 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="5">
+        <v>20140808</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" t="s">
         <v>11</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="6">
-        <v>20140808</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="11">
         <v>49.51634069</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="12">
         <v>27.18025613</v>
       </c>
       <c r="I25">
@@ -3405,28 +3396,28 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="6">
+        <v>20094613</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" t="s">
         <v>11</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="E26" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="3">
-        <v>20094613</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="9">
         <v>49.516153760000002</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="10">
         <v>27.18014324</v>
       </c>
       <c r="I26">
@@ -3443,28 +3434,28 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="7">
+        <v>20109009</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" t="s">
         <v>11</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="E27" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="7">
-        <v>20109009</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="11">
         <v>49.515998940000003</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="12">
         <v>27.180020760000001</v>
       </c>
       <c r="I27">
@@ -3481,28 +3472,28 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="6">
+        <v>20094609</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" t="s">
         <v>11</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="E28" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="3">
-        <v>20094609</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="9">
         <v>49.515846809999999</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="10">
         <v>27.1798936</v>
       </c>
       <c r="I28">
@@ -3519,28 +3510,28 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="7">
+        <v>20077505</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="B29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="7">
-        <v>20077505</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="11">
         <v>49.515698759999999</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <v>27.179762910000001</v>
       </c>
       <c r="I29">
@@ -3557,28 +3548,28 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="6">
+        <v>20094610</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" t="s">
         <v>11</v>
       </c>
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="3">
-        <v>20094610</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="9">
         <v>49.515554799999997</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="10">
         <v>27.17962872</v>
       </c>
       <c r="I30">
@@ -3595,28 +3586,28 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="7">
+        <v>20109971</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" t="s">
         <v>11</v>
       </c>
-      <c r="B31" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="7">
-        <v>20109971</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="11">
         <v>49.515414880000002</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="12">
         <v>27.179490980000001</v>
       </c>
       <c r="I31">
@@ -3633,28 +3624,28 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="6">
+        <v>20079025</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="3">
-        <v>20079025</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="9">
         <v>49.515225520000001</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="10">
         <v>27.179291889999998</v>
       </c>
       <c r="I32">
@@ -3671,28 +3662,28 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="7">
+        <v>20094865</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C33" t="s">
         <v>11</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="E33" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="7">
-        <v>20094865</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="11">
         <v>49.515108079999997</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <v>27.179160190000001</v>
       </c>
       <c r="I33">
@@ -3709,28 +3700,28 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="6">
+        <v>20094898</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" t="s">
         <v>11</v>
       </c>
-      <c r="B34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="3">
-        <v>20094898</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="9">
         <v>49.514989030000002</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="10">
         <v>27.179019570000001</v>
       </c>
       <c r="I34">
@@ -3747,28 +3738,28 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="4">
+        <v>20131058</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C35" t="s">
         <v>11</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="E35" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="2">
-        <v>20131058</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="9">
         <v>49.52641045</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="10">
         <v>27.173567590000001</v>
       </c>
       <c r="I35">
@@ -3785,28 +3776,28 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="5">
+        <v>20105668</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" t="s">
         <v>11</v>
       </c>
-      <c r="B36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="6">
-        <v>20105668</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="11">
         <v>49.526528650000003</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="12">
         <v>27.173426899999999</v>
       </c>
       <c r="I36">
@@ -3823,28 +3814,28 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="6">
+        <v>20109831</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37" t="s">
         <v>11</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="E37" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="3">
-        <v>20109831</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="9">
         <v>49.526646849999999</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="10">
         <v>27.173286210000001</v>
       </c>
       <c r="I37">
@@ -3861,28 +3852,28 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="7">
+        <v>20139066</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C38" t="s">
         <v>11</v>
       </c>
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="7">
-        <v>20139066</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="11">
         <v>49.526765650000002</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="12">
         <v>27.173147199999999</v>
       </c>
       <c r="I38">
@@ -3899,28 +3890,28 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="6">
+        <v>20132504</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C39" t="s">
         <v>11</v>
       </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="3">
-        <v>20132504</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="9">
         <v>49.526885280000002</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="10">
         <v>27.173004880000001</v>
       </c>
       <c r="I39">
@@ -3937,28 +3928,28 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="7">
+        <v>20108195</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C40" t="s">
         <v>11</v>
       </c>
-      <c r="B40" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="7">
-        <v>20108195</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="11">
         <v>49.52700145</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="12">
         <v>27.172864140000001</v>
       </c>
       <c r="I40">
@@ -3975,28 +3966,28 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="6">
+        <v>20105644</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" t="s">
         <v>11</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="E41" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="3">
-        <v>20105644</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="9">
         <v>49.527135540000003</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="10">
         <v>27.172704540000002</v>
       </c>
       <c r="I41">
@@ -4013,28 +4004,28 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="7">
+        <v>20133642</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" t="s">
         <v>61</v>
       </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="7">
-        <v>20133642</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="11">
         <v>49.526124750000001</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="12">
         <v>27.173339410000001</v>
       </c>
       <c r="I42">
@@ -4051,28 +4042,28 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="6">
+        <v>20141021</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" t="s">
         <v>61</v>
       </c>
-      <c r="B43" t="s">
+      <c r="D43" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="E43" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="3">
-        <v>20141021</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="9">
         <v>49.52596844</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="10">
         <v>27.173233419999999</v>
       </c>
       <c r="I43">
@@ -4089,28 +4080,28 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="7">
+        <v>20113059</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" t="s">
         <v>61</v>
       </c>
-      <c r="B44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="7">
-        <v>20113059</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="11">
         <v>49.525811130000001</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="12">
         <v>27.173127709999999</v>
       </c>
       <c r="I44">
@@ -4127,28 +4118,28 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="6">
+        <v>20129551</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" t="s">
         <v>61</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="E45" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="3">
-        <v>20129551</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="9">
         <v>49.525653820000002</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="10">
         <v>27.173022</v>
       </c>
       <c r="I45">
@@ -4165,28 +4156,28 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46">
+        <v>20123858</v>
+      </c>
+      <c r="B46" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" t="s">
         <v>61</v>
       </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="10">
-        <v>20123858</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="8">
         <v>49.53214011</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="8">
         <v>27.166738930000001</v>
       </c>
       <c r="I46">
@@ -4203,28 +4194,28 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47">
+        <v>20113486</v>
+      </c>
+      <c r="B47" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="E47" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="10">
-        <v>20113486</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="8">
         <v>49.532258239999997</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="8">
         <v>27.166600119999998</v>
       </c>
       <c r="I47">
@@ -4241,28 +4232,28 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48">
+        <v>20128376</v>
+      </c>
+      <c r="B48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" t="s">
         <v>61</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="E48" t="s">
         <v>68</v>
       </c>
-      <c r="D48" s="10">
-        <v>20128376</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="8">
         <v>49.532375940000001</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="8">
         <v>27.166460010000002</v>
       </c>
       <c r="I48">
@@ -4279,28 +4270,28 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49">
+        <v>20131437</v>
+      </c>
+      <c r="B49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" t="s">
         <v>61</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="E49" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="10">
-        <v>20131437</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="8">
         <v>49.532493780000003</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="8">
         <v>27.166319990000002</v>
       </c>
       <c r="I49">
@@ -4317,28 +4308,28 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50">
+        <v>20131607</v>
+      </c>
+      <c r="B50" t="s">
+        <v>273</v>
+      </c>
+      <c r="C50" t="s">
         <v>61</v>
       </c>
-      <c r="B50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
         <v>70</v>
       </c>
-      <c r="D50" s="10">
-        <v>20131607</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="8">
         <v>49.532611529999997</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="8">
         <v>27.166179929999998</v>
       </c>
       <c r="I50">
@@ -4355,28 +4346,28 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51">
+        <v>20138706</v>
+      </c>
+      <c r="B51" t="s">
+        <v>275</v>
+      </c>
+      <c r="C51" t="s">
         <v>61</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="E51" t="s">
         <v>71</v>
       </c>
-      <c r="D51" s="10">
-        <v>20138706</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="8">
         <v>49.532729230000001</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="8">
         <v>27.166039810000001</v>
       </c>
       <c r="I51">
@@ -4393,28 +4384,28 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52">
+        <v>20130103</v>
+      </c>
+      <c r="B52" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" t="s">
         <v>61</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="E52" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="10">
-        <v>20130103</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="8">
         <v>49.532846880000001</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="8">
         <v>27.165899700000001</v>
       </c>
       <c r="I52">
@@ -4431,28 +4422,28 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53">
+        <v>20132482</v>
+      </c>
+      <c r="B53" t="s">
+        <v>279</v>
+      </c>
+      <c r="C53" t="s">
         <v>61</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="E53" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="10">
-        <v>20132482</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="8">
         <v>49.532964499999999</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="8">
         <v>27.165759510000001</v>
       </c>
       <c r="I53">
@@ -4469,28 +4460,28 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54">
+        <v>20139028</v>
+      </c>
+      <c r="B54" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" t="s">
         <v>61</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="E54" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="10">
-        <v>20139028</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="8">
         <v>49.53313868</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="8">
         <v>27.165552040000001</v>
       </c>
       <c r="I54">
@@ -4507,28 +4498,28 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55">
+        <v>20134235</v>
+      </c>
+      <c r="B55" t="s">
+        <v>283</v>
+      </c>
+      <c r="C55" t="s">
         <v>61</v>
       </c>
-      <c r="B55" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="10">
-        <v>20134235</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="8">
         <v>49.533273059999999</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="8">
         <v>27.16539216</v>
       </c>
       <c r="I55">
@@ -4545,28 +4536,28 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56">
+        <v>20133746</v>
+      </c>
+      <c r="B56" t="s">
+        <v>285</v>
+      </c>
+      <c r="C56" t="s">
         <v>61</v>
       </c>
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="10">
-        <v>20133746</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="8">
         <v>49.533407990000001</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="8">
         <v>27.1652339</v>
       </c>
       <c r="I56">
@@ -4583,28 +4574,28 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57">
+        <v>20103449</v>
+      </c>
+      <c r="B57" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" t="s">
         <v>61</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="E57" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="10">
-        <v>20103449</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="8">
         <v>49.560424410000003</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="8">
         <v>27.16142722</v>
       </c>
       <c r="I57">
@@ -4621,28 +4612,28 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58">
+        <v>20084171</v>
+      </c>
+      <c r="B58" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" t="s">
         <v>61</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="E58" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="10">
-        <v>20084171</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G58" s="11">
+      <c r="G58" s="8">
         <v>49.563266609999999</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H58" s="8">
         <v>27.151956259999999</v>
       </c>
       <c r="I58">
@@ -4659,28 +4650,28 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59">
+        <v>20160149</v>
+      </c>
+      <c r="B59" t="s">
+        <v>291</v>
+      </c>
+      <c r="C59" t="s">
         <v>61</v>
       </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="10">
-        <v>20160149</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G59" s="8">
         <v>49.5622495</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="8">
         <v>27.149089379999999</v>
       </c>
       <c r="I59">
@@ -4697,28 +4688,28 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60">
+        <v>20057113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" t="s">
         <v>61</v>
       </c>
-      <c r="B60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="10">
-        <v>20057113</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="8">
         <v>49.554131060000003</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H60" s="8">
         <v>27.157392340000001</v>
       </c>
       <c r="I60">
@@ -4735,28 +4726,28 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61">
+        <v>20012917</v>
+      </c>
+      <c r="B61" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" t="s">
         <v>61</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="E61" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="10">
-        <v>20012917</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G61" s="8">
         <v>49.553849229999997</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="8">
         <v>27.157409479999998</v>
       </c>
       <c r="I61">
@@ -4773,28 +4764,28 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62">
+        <v>20106928</v>
+      </c>
+      <c r="B62" t="s">
+        <v>250</v>
+      </c>
+      <c r="C62" t="s">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="D62" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="E62" t="s">
         <v>82</v>
       </c>
-      <c r="D62" s="10">
-        <v>20106928</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="8">
         <v>49.553641560000003</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="8">
         <v>27.15729704</v>
       </c>
       <c r="I62">
@@ -4811,28 +4802,28 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63">
+        <v>20015220</v>
+      </c>
+      <c r="B63" t="s">
+        <v>298</v>
+      </c>
+      <c r="C63" t="s">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" t="s">
         <v>83</v>
       </c>
-      <c r="D63" s="10">
-        <v>20015220</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G63" s="8">
         <v>49.553427489999997</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="8">
         <v>27.157177449999999</v>
       </c>
       <c r="I63">
@@ -4849,28 +4840,28 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64">
+        <v>20030607</v>
+      </c>
+      <c r="B64" t="s">
+        <v>300</v>
+      </c>
+      <c r="C64" t="s">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" t="s">
         <v>84</v>
       </c>
-      <c r="D64" s="10">
-        <v>20030607</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="F64" s="10" t="s">
+      <c r="F64" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="8">
         <v>49.554323629999999</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="8">
         <v>27.157156619999999</v>
       </c>
       <c r="I64">
@@ -4887,28 +4878,28 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65">
+        <v>20135522</v>
+      </c>
+      <c r="B65" t="s">
+        <v>302</v>
+      </c>
+      <c r="C65" t="s">
         <v>61</v>
       </c>
-      <c r="B65" t="s">
-        <v>19</v>
-      </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" t="s">
         <v>85</v>
       </c>
-      <c r="D65" s="10">
-        <v>20135522</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G65" s="8">
         <v>49.55414047</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="8">
         <v>27.156950559999999</v>
       </c>
       <c r="I65">
@@ -4925,28 +4916,28 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66">
+        <v>20132194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" t="s">
         <v>61</v>
       </c>
-      <c r="B66" t="s">
+      <c r="D66" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="E66" t="s">
         <v>86</v>
       </c>
-      <c r="D66" s="10">
-        <v>20132194</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="8">
         <v>49.554481719999998</v>
       </c>
-      <c r="H66" s="11">
+      <c r="H66" s="8">
         <v>27.156900310000001</v>
       </c>
       <c r="I66">
@@ -4963,28 +4954,28 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67">
+        <v>20002293</v>
+      </c>
+      <c r="B67" t="s">
+        <v>305</v>
+      </c>
+      <c r="C67" t="s">
         <v>61</v>
       </c>
-      <c r="B67" t="s">
+      <c r="D67" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="E67" t="s">
         <v>87</v>
       </c>
-      <c r="D67" s="10">
-        <v>20002293</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G67" s="8">
         <v>49.554222019999997</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="8">
         <v>27.156726259999999</v>
       </c>
       <c r="I67">
@@ -5001,28 +4992,28 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68">
+        <v>20084602</v>
+      </c>
+      <c r="B68" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" t="s">
         <v>61</v>
       </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="E68" t="s">
         <v>88</v>
       </c>
-      <c r="D68" s="10">
-        <v>20084602</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="8">
         <v>49.554016490000002</v>
       </c>
-      <c r="H68" s="11">
+      <c r="H68" s="8">
         <v>27.156611760000001</v>
       </c>
       <c r="I68">
@@ -5039,28 +5030,28 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69">
+        <v>20013799</v>
+      </c>
+      <c r="B69" t="s">
+        <v>309</v>
+      </c>
+      <c r="C69" t="s">
         <v>61</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="E69" t="s">
         <v>89</v>
       </c>
-      <c r="D69" s="10">
-        <v>20013799</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="8">
         <v>49.554666099999999</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="8">
         <v>27.156758450000002</v>
       </c>
       <c r="I69">
@@ -5077,28 +5068,28 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70">
+        <v>20084489</v>
+      </c>
+      <c r="B70" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" t="s">
         <v>61</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="E70" t="s">
         <v>90</v>
       </c>
-      <c r="D70" s="10">
-        <v>20084489</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="8">
         <v>49.56261765</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="8">
         <v>27.14073995</v>
       </c>
       <c r="I70">
@@ -5115,28 +5106,28 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71">
+        <v>20110454</v>
+      </c>
+      <c r="B71" t="s">
+        <v>240</v>
+      </c>
+      <c r="C71" t="s">
         <v>61</v>
       </c>
-      <c r="B71" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
         <v>91</v>
       </c>
-      <c r="D71" s="10">
-        <v>20110454</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="8">
         <v>49.562526439999999</v>
       </c>
-      <c r="H71" s="11">
+      <c r="H71" s="8">
         <v>27.140533720000001</v>
       </c>
       <c r="I71">
@@ -5153,28 +5144,28 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72">
+        <v>20013182</v>
+      </c>
+      <c r="B72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C72" t="s">
         <v>61</v>
       </c>
-      <c r="B72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
         <v>92</v>
       </c>
-      <c r="D72" s="10">
-        <v>20013182</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G72" s="11">
+      <c r="G72" s="8">
         <v>49.562389600000003</v>
       </c>
-      <c r="H72" s="11">
+      <c r="H72" s="8">
         <v>27.140376830000001</v>
       </c>
       <c r="I72">
@@ -5191,28 +5182,28 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73">
+        <v>20014361</v>
+      </c>
+      <c r="B73" t="s">
+        <v>316</v>
+      </c>
+      <c r="C73" t="s">
         <v>61</v>
       </c>
-      <c r="B73" t="s">
-        <v>19</v>
-      </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
         <v>93</v>
       </c>
-      <c r="D73" s="10">
-        <v>20014361</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G73" s="11">
+      <c r="G73" s="8">
         <v>49.562932959999998</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="8">
         <v>27.140518369999999</v>
       </c>
       <c r="I73">
@@ -5229,28 +5220,28 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74">
+        <v>20110274</v>
+      </c>
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74" t="s">
         <v>61</v>
       </c>
-      <c r="B74" t="s">
+      <c r="D74" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="E74" t="s">
         <v>94</v>
       </c>
-      <c r="D74" s="10">
-        <v>20110274</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F74" s="10" t="s">
+      <c r="F74" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="G74" s="11">
+      <c r="G74" s="8">
         <v>49.562724879999998</v>
       </c>
-      <c r="H74" s="11">
+      <c r="H74" s="8">
         <v>27.14039425</v>
       </c>
       <c r="I74">
@@ -5267,28 +5258,28 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75">
+        <v>20084582</v>
+      </c>
+      <c r="B75" t="s">
+        <v>319</v>
+      </c>
+      <c r="C75" t="s">
         <v>61</v>
       </c>
-      <c r="B75" t="s">
-        <v>19</v>
-      </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
         <v>95</v>
       </c>
-      <c r="D75" s="10">
-        <v>20084582</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G75" s="11">
+      <c r="G75" s="8">
         <v>49.56258776</v>
       </c>
-      <c r="H75" s="11">
+      <c r="H75" s="8">
         <v>27.140238490000002</v>
       </c>
       <c r="I75">
@@ -5305,28 +5296,28 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76">
+        <v>20012812</v>
+      </c>
+      <c r="B76" t="s">
+        <v>321</v>
+      </c>
+      <c r="C76" t="s">
         <v>61</v>
       </c>
-      <c r="B76" t="s">
+      <c r="D76" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="E76" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="10">
-        <v>20012812</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="G76" s="11">
+      <c r="G76" s="8">
         <v>49.563254290000003</v>
       </c>
-      <c r="H76" s="11">
+      <c r="H76" s="8">
         <v>27.140293369999998</v>
       </c>
       <c r="I76">
@@ -5343,28 +5334,28 @@
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77">
+        <v>20041581</v>
+      </c>
+      <c r="B77" t="s">
+        <v>323</v>
+      </c>
+      <c r="C77" t="s">
         <v>61</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="E77" t="s">
         <v>97</v>
       </c>
-      <c r="D77" s="10">
-        <v>20041581</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="F77" s="10" t="s">
+      <c r="F77" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="G77" s="11">
+      <c r="G77" s="8">
         <v>49.563201829999997</v>
       </c>
-      <c r="H77" s="11">
+      <c r="H77" s="8">
         <v>27.14008316</v>
       </c>
       <c r="I77">
@@ -5381,28 +5372,28 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78">
+        <v>20014555</v>
+      </c>
+      <c r="B78" t="s">
+        <v>325</v>
+      </c>
+      <c r="C78" t="s">
         <v>61</v>
       </c>
-      <c r="B78" t="s">
-        <v>19</v>
-      </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
         <v>98</v>
       </c>
-      <c r="D78" s="10">
-        <v>20014555</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F78" s="10" t="s">
+      <c r="F78" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G78" s="11">
+      <c r="G78" s="8">
         <v>49.563064500000003</v>
       </c>
-      <c r="H78" s="11">
+      <c r="H78" s="8">
         <v>27.139926760000002</v>
       </c>
       <c r="I78">
@@ -5419,28 +5410,28 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79">
+        <v>20077308</v>
+      </c>
+      <c r="B79" t="s">
+        <v>327</v>
+      </c>
+      <c r="C79" t="s">
         <v>61</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
         <v>12</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="E79" t="s">
         <v>99</v>
       </c>
-      <c r="D79" s="10">
-        <v>20077308</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F79" s="10" t="s">
+      <c r="F79" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G79" s="11">
+      <c r="G79" s="8">
         <v>49.563451229999998</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H79" s="8">
         <v>27.140075079999999</v>
       </c>
       <c r="I79">
@@ -5457,28 +5448,28 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80">
+        <v>20012759</v>
+      </c>
+      <c r="B80" t="s">
+        <v>329</v>
+      </c>
+      <c r="C80" t="s">
         <v>61</v>
       </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" t="s">
         <v>100</v>
       </c>
-      <c r="D80" s="10">
-        <v>20012759</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="8">
         <v>49.563242279999997</v>
       </c>
-      <c r="H80" s="11">
+      <c r="H80" s="8">
         <v>27.13983636</v>
       </c>
       <c r="I80">
@@ -5495,28 +5486,28 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81">
+        <v>20044351</v>
+      </c>
+      <c r="B81" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" t="s">
         <v>61</v>
       </c>
-      <c r="B81" t="s">
+      <c r="D81" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="E81" t="s">
         <v>101</v>
       </c>
-      <c r="D81" s="10">
-        <v>20044351</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F81" s="10" t="s">
+      <c r="F81" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G81" s="11">
+      <c r="G81" s="8">
         <v>49.545621500000003</v>
       </c>
-      <c r="H81" s="11">
+      <c r="H81" s="8">
         <v>27.150425479999999</v>
       </c>
       <c r="I81">
@@ -5533,28 +5524,28 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82">
+        <v>20012709</v>
+      </c>
+      <c r="B82" t="s">
+        <v>333</v>
+      </c>
+      <c r="C82" t="s">
         <v>102</v>
       </c>
-      <c r="B82" t="s">
+      <c r="D82" t="s">
         <v>12</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="E82" t="s">
         <v>103</v>
       </c>
-      <c r="D82" s="10">
-        <v>20012709</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F82" s="10" t="s">
+      <c r="F82" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G82" s="11">
+      <c r="G82" s="8">
         <v>49.545935280000002</v>
       </c>
-      <c r="H82" s="11">
+      <c r="H82" s="8">
         <v>27.150364</v>
       </c>
       <c r="I82">
@@ -5571,28 +5562,28 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83">
+        <v>20014399</v>
+      </c>
+      <c r="B83" t="s">
+        <v>335</v>
+      </c>
+      <c r="C83" t="s">
         <v>102</v>
       </c>
-      <c r="B83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" t="s">
         <v>104</v>
       </c>
-      <c r="D83" s="10">
-        <v>20014399</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F83" s="10" t="s">
+      <c r="F83" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="G83" s="11">
+      <c r="G83" s="8">
         <v>49.546142709999998</v>
       </c>
-      <c r="H83" s="11">
+      <c r="H83" s="8">
         <v>27.150323310000001</v>
       </c>
       <c r="I83">
@@ -5609,28 +5600,28 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84">
+        <v>20108835</v>
+      </c>
+      <c r="B84" t="s">
+        <v>337</v>
+      </c>
+      <c r="C84" t="s">
         <v>102</v>
       </c>
-      <c r="B84" t="s">
+      <c r="D84" t="s">
         <v>12</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="E84" t="s">
         <v>105</v>
       </c>
-      <c r="D84" s="10">
-        <v>20108835</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="F84" s="10" t="s">
+      <c r="F84" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="8">
         <v>49.546362100000003</v>
       </c>
-      <c r="H84" s="11">
+      <c r="H84" s="8">
         <v>27.1502801</v>
       </c>
       <c r="I84">
@@ -5647,28 +5638,28 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85">
+        <v>20013815</v>
+      </c>
+      <c r="B85" t="s">
+        <v>339</v>
+      </c>
+      <c r="C85" t="s">
         <v>102</v>
       </c>
-      <c r="B85" t="s">
+      <c r="D85" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="E85" t="s">
         <v>106</v>
       </c>
-      <c r="D85" s="10">
-        <v>20013815</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="G85" s="11">
+      <c r="G85" s="8">
         <v>49.546658399999998</v>
       </c>
-      <c r="H85" s="11">
+      <c r="H85" s="8">
         <v>27.150221899999998</v>
       </c>
       <c r="I85">
@@ -5685,28 +5676,28 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86">
+        <v>20167276</v>
+      </c>
+      <c r="B86" t="s">
+        <v>341</v>
+      </c>
+      <c r="C86" t="s">
         <v>102</v>
       </c>
-      <c r="B86" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" t="s">
         <v>107</v>
       </c>
-      <c r="D86" s="10">
-        <v>20167276</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F86" s="10" t="s">
+      <c r="F86" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G86" s="11">
+      <c r="G86" s="8">
         <v>49.547308200000003</v>
       </c>
-      <c r="H86" s="11">
+      <c r="H86" s="8">
         <v>27.150100640000002</v>
       </c>
       <c r="I86">
@@ -5723,28 +5714,28 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87">
+        <v>20108827</v>
+      </c>
+      <c r="B87" t="s">
+        <v>337</v>
+      </c>
+      <c r="C87" t="s">
         <v>102</v>
       </c>
-      <c r="B87" t="s">
-        <v>19</v>
-      </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" t="s">
         <v>108</v>
       </c>
-      <c r="D87" s="10">
-        <v>20108827</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="8">
         <v>49.547677530000001</v>
       </c>
-      <c r="H87" s="11">
+      <c r="H87" s="8">
         <v>27.149913250000001</v>
       </c>
       <c r="I87">
@@ -5761,28 +5752,28 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88">
+        <v>20112838</v>
+      </c>
+      <c r="B88" t="s">
+        <v>189</v>
+      </c>
+      <c r="C88" t="s">
         <v>102</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="E88" t="s">
         <v>109</v>
       </c>
-      <c r="D88" s="10">
-        <v>20112838</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G88" s="11">
+      <c r="G88" s="8">
         <v>49.545428630000004</v>
       </c>
-      <c r="H88" s="11">
+      <c r="H88" s="8">
         <v>27.149994710000001</v>
       </c>
       <c r="I88">
@@ -5799,28 +5790,28 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89">
+        <v>20109684</v>
+      </c>
+      <c r="B89" t="s">
+        <v>198</v>
+      </c>
+      <c r="C89" t="s">
         <v>102</v>
       </c>
-      <c r="B89" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" t="s">
         <v>110</v>
       </c>
-      <c r="D89" s="10">
-        <v>20109684</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G89" s="11">
+      <c r="G89" s="8">
         <v>49.545310450000002</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="8">
         <v>27.149544469999999</v>
       </c>
       <c r="I89">
@@ -5837,28 +5828,28 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90">
+        <v>20107501</v>
+      </c>
+      <c r="B90" t="s">
+        <v>346</v>
+      </c>
+      <c r="C90" t="s">
         <v>102</v>
       </c>
-      <c r="B90" t="s">
+      <c r="D90" t="s">
         <v>12</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="E90" t="s">
         <v>111</v>
       </c>
-      <c r="D90" s="10">
-        <v>20107501</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F90" s="10" t="s">
+      <c r="F90" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G90" s="11">
+      <c r="G90" s="8">
         <v>49.54582877</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="8">
         <v>27.14983947</v>
       </c>
       <c r="I90">
@@ -5875,28 +5866,28 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91">
+        <v>20039251</v>
+      </c>
+      <c r="B91" t="s">
+        <v>348</v>
+      </c>
+      <c r="C91" t="s">
         <v>102</v>
       </c>
-      <c r="B91" t="s">
-        <v>19</v>
-      </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" t="s">
         <v>112</v>
       </c>
-      <c r="D91" s="10">
-        <v>20039251</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F91" s="10" t="s">
+      <c r="F91" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="8">
         <v>49.545731809999999</v>
       </c>
-      <c r="H91" s="11">
+      <c r="H91" s="8">
         <v>27.149462</v>
       </c>
       <c r="I91">
@@ -5913,28 +5904,28 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92">
+        <v>20014566</v>
+      </c>
+      <c r="B92" t="s">
+        <v>350</v>
+      </c>
+      <c r="C92" t="s">
         <v>102</v>
       </c>
-      <c r="B92" t="s">
-        <v>19</v>
-      </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" t="s">
         <v>113</v>
       </c>
-      <c r="D92" s="10">
-        <v>20014566</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="F92" s="10" t="s">
+      <c r="F92" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="G92" s="11">
+      <c r="G92" s="8">
         <v>49.556905989999997</v>
       </c>
-      <c r="H92" s="11">
+      <c r="H92" s="8">
         <v>27.133803289999999</v>
       </c>
       <c r="I92">
@@ -5951,28 +5942,28 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93">
+        <v>20071660</v>
+      </c>
+      <c r="B93" t="s">
+        <v>352</v>
+      </c>
+      <c r="C93" t="s">
         <v>102</v>
       </c>
-      <c r="B93" t="s">
+      <c r="D93" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="E93" t="s">
         <v>114</v>
       </c>
-      <c r="D93" s="10">
-        <v>20071660</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G93" s="11">
+      <c r="G93" s="8">
         <v>49.556634240000001</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="8">
         <v>27.13373369</v>
       </c>
       <c r="I93">
@@ -5989,28 +5980,28 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94">
+        <v>20001537</v>
+      </c>
+      <c r="B94" t="s">
+        <v>354</v>
+      </c>
+      <c r="C94" t="s">
         <v>102</v>
       </c>
-      <c r="B94" t="s">
+      <c r="D94" t="s">
         <v>12</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="E94" t="s">
         <v>115</v>
       </c>
-      <c r="D94" s="10">
-        <v>20001537</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="F94" s="10" t="s">
+      <c r="F94" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="G94" s="11">
+      <c r="G94" s="8">
         <v>49.557344669999999</v>
       </c>
-      <c r="H94" s="11">
+      <c r="H94" s="8">
         <v>27.13325949</v>
       </c>
       <c r="I94">
@@ -6027,28 +6018,28 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95">
+        <v>20109056</v>
+      </c>
+      <c r="B95" t="s">
+        <v>232</v>
+      </c>
+      <c r="C95" t="s">
         <v>102</v>
       </c>
-      <c r="B95" t="s">
-        <v>19</v>
-      </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" t="s">
         <v>116</v>
       </c>
-      <c r="D95" s="10">
-        <v>20109056</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F95" s="10" t="s">
+      <c r="F95" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G95" s="8">
         <v>49.557155459999997</v>
       </c>
-      <c r="H95" s="11">
+      <c r="H95" s="8">
         <v>27.13315575</v>
       </c>
       <c r="I95">
@@ -6065,28 +6056,28 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96">
+        <v>20076804</v>
+      </c>
+      <c r="B96" t="s">
+        <v>357</v>
+      </c>
+      <c r="C96" t="s">
         <v>102</v>
       </c>
-      <c r="B96" t="s">
+      <c r="D96" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="E96" t="s">
         <v>117</v>
       </c>
-      <c r="D96" s="10">
-        <v>20076804</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="F96" s="10" t="s">
+      <c r="F96" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="G96" s="11">
+      <c r="G96" s="8">
         <v>49.557653539999997</v>
       </c>
-      <c r="H96" s="11">
+      <c r="H96" s="8">
         <v>27.133049880000002</v>
       </c>
       <c r="I96">
@@ -6103,28 +6094,28 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97">
+        <v>20013015</v>
+      </c>
+      <c r="B97" t="s">
+        <v>359</v>
+      </c>
+      <c r="C97" t="s">
         <v>102</v>
       </c>
-      <c r="B97" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" t="s">
         <v>118</v>
       </c>
-      <c r="D97" s="10">
-        <v>20013015</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="F97" s="10" t="s">
+      <c r="F97" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="G97" s="11">
+      <c r="G97" s="8">
         <v>49.557304960000003</v>
       </c>
-      <c r="H97" s="11">
+      <c r="H97" s="8">
         <v>27.132988990000001</v>
       </c>
       <c r="I97">
@@ -6141,28 +6132,28 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98">
+        <v>20013503</v>
+      </c>
+      <c r="B98" t="s">
+        <v>361</v>
+      </c>
+      <c r="C98" t="s">
         <v>102</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
         <v>12</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="E98" t="s">
         <v>119</v>
       </c>
-      <c r="D98" s="10">
-        <v>20013503</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="F98" s="10" t="s">
+      <c r="F98" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="G98" s="11">
+      <c r="G98" s="8">
         <v>49.557394559999999</v>
       </c>
-      <c r="H98" s="11">
+      <c r="H98" s="8">
         <v>27.132858169999999</v>
       </c>
       <c r="I98">
@@ -6179,28 +6170,28 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99">
+        <v>20002228</v>
+      </c>
+      <c r="B99" t="s">
+        <v>363</v>
+      </c>
+      <c r="C99" t="s">
         <v>102</v>
       </c>
-      <c r="B99" t="s">
-        <v>19</v>
-      </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" t="s">
         <v>120</v>
       </c>
-      <c r="D99" s="10">
-        <v>20002228</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="F99" s="10" t="s">
+      <c r="F99" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="G99" s="11">
+      <c r="G99" s="8">
         <v>49.55780807</v>
       </c>
-      <c r="H99" s="11">
+      <c r="H99" s="8">
         <v>27.132824450000001</v>
       </c>
       <c r="I99">
@@ -6217,28 +6208,28 @@
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100">
+        <v>20076560</v>
+      </c>
+      <c r="B100" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" t="s">
         <v>102</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="E100" t="s">
         <v>121</v>
       </c>
-      <c r="D100" s="10">
-        <v>20076560</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="F100" s="10" t="s">
+      <c r="F100" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="G100" s="11">
+      <c r="G100" s="8">
         <v>49.557484199999998</v>
       </c>
-      <c r="H100" s="11">
+      <c r="H100" s="8">
         <v>27.132727360000001</v>
       </c>
       <c r="I100">
@@ -6255,28 +6246,28 @@
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101">
+        <v>20012518</v>
+      </c>
+      <c r="B101" t="s">
+        <v>367</v>
+      </c>
+      <c r="C101" t="s">
         <v>102</v>
       </c>
-      <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" t="s">
         <v>122</v>
       </c>
-      <c r="D101" s="10">
-        <v>20012518</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="F101" s="10" t="s">
+      <c r="F101" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="G101" s="11">
+      <c r="G101" s="8">
         <v>49.557897760000003</v>
       </c>
-      <c r="H101" s="11">
+      <c r="H101" s="8">
         <v>27.13269373</v>
       </c>
       <c r="I101">
@@ -6293,28 +6284,28 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102">
+        <v>20014475</v>
+      </c>
+      <c r="B102" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" t="s">
         <v>102</v>
       </c>
-      <c r="B102" t="s">
+      <c r="D102" t="s">
         <v>12</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="E102" t="s">
         <v>123</v>
       </c>
-      <c r="D102" s="10">
-        <v>20014475</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F102" s="10" t="s">
+      <c r="F102" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G102" s="11">
+      <c r="G102" s="8">
         <v>49.55757388</v>
       </c>
-      <c r="H102" s="11">
+      <c r="H102" s="8">
         <v>27.13259661</v>
       </c>
       <c r="I102">
@@ -6331,28 +6322,28 @@
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103">
+        <v>20135553</v>
+      </c>
+      <c r="B103" t="s">
+        <v>371</v>
+      </c>
+      <c r="C103" t="s">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" t="s">
         <v>124</v>
       </c>
-      <c r="D103" s="10">
-        <v>20135553</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="F103" s="10" t="s">
+      <c r="F103" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="G103" s="11">
+      <c r="G103" s="8">
         <v>49.578451540000003</v>
       </c>
-      <c r="H103" s="11">
+      <c r="H103" s="8">
         <v>27.175913049999998</v>
       </c>
       <c r="I103">
@@ -6369,28 +6360,28 @@
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104">
+        <v>20107602</v>
+      </c>
+      <c r="B104" t="s">
+        <v>346</v>
+      </c>
+      <c r="C104" t="s">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
-        <v>19</v>
-      </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" t="s">
         <v>125</v>
       </c>
-      <c r="D104" s="10">
-        <v>20107602</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F104" s="10" t="s">
+      <c r="F104" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="G104" s="11">
+      <c r="G104" s="8">
         <v>49.578316749999999</v>
       </c>
-      <c r="H104" s="11">
+      <c r="H104" s="8">
         <v>27.175778099999999</v>
       </c>
       <c r="I104">
@@ -6407,28 +6398,28 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105">
+        <v>20081600</v>
+      </c>
+      <c r="B105" t="s">
+        <v>374</v>
+      </c>
+      <c r="C105" t="s">
         <v>102</v>
       </c>
-      <c r="B105" t="s">
-        <v>19</v>
-      </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" t="s">
         <v>126</v>
       </c>
-      <c r="D105" s="10">
-        <v>20081600</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F105" s="10" t="s">
+      <c r="F105" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G105" s="11">
+      <c r="G105" s="8">
         <v>49.578181120000004</v>
       </c>
-      <c r="H105" s="11">
+      <c r="H105" s="8">
         <v>27.17564453</v>
       </c>
       <c r="I105">
@@ -6445,28 +6436,28 @@
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106">
+        <v>20139668</v>
+      </c>
+      <c r="B106" t="s">
+        <v>376</v>
+      </c>
+      <c r="C106" t="s">
         <v>102</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
         <v>12</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="E106" t="s">
         <v>127</v>
       </c>
-      <c r="D106" s="10">
-        <v>20139668</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="F106" s="10" t="s">
+      <c r="F106" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="G106" s="11">
+      <c r="G106" s="8">
         <v>49.57804531</v>
       </c>
-      <c r="H106" s="11">
+      <c r="H106" s="8">
         <v>27.175511</v>
       </c>
       <c r="I106">
@@ -6483,28 +6474,28 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107">
+        <v>20083810</v>
+      </c>
+      <c r="B107" t="s">
+        <v>378</v>
+      </c>
+      <c r="C107" t="s">
         <v>102</v>
       </c>
-      <c r="B107" t="s">
-        <v>19</v>
-      </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" t="s">
         <v>128</v>
       </c>
-      <c r="D107" s="10">
-        <v>20083810</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F107" s="10" t="s">
+      <c r="F107" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="G107" s="11">
+      <c r="G107" s="8">
         <v>49.577909560000002</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="8">
         <v>27.17537746</v>
       </c>
       <c r="I107">
@@ -6521,28 +6512,28 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108">
+        <v>20138413</v>
+      </c>
+      <c r="B108" t="s">
+        <v>380</v>
+      </c>
+      <c r="C108" t="s">
         <v>102</v>
       </c>
-      <c r="B108" t="s">
-        <v>19</v>
-      </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
         <v>129</v>
       </c>
-      <c r="D108" s="10">
-        <v>20138413</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="F108" s="10" t="s">
+      <c r="F108" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="G108" s="11">
+      <c r="G108" s="8">
         <v>49.577773870000001</v>
       </c>
-      <c r="H108" s="11">
+      <c r="H108" s="8">
         <v>27.175243900000002</v>
       </c>
       <c r="I108">
@@ -6559,28 +6550,28 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109">
+        <v>20115161</v>
+      </c>
+      <c r="B109" t="s">
+        <v>232</v>
+      </c>
+      <c r="C109" t="s">
         <v>102</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
         <v>12</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="E109" t="s">
         <v>130</v>
       </c>
-      <c r="D109" s="10">
-        <v>20115161</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F109" s="10" t="s">
+      <c r="F109" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="G109" s="11">
+      <c r="G109" s="8">
         <v>49.577597500000003</v>
       </c>
-      <c r="H109" s="11">
+      <c r="H109" s="8">
         <v>27.175070170000001</v>
       </c>
       <c r="I109">
@@ -6597,28 +6588,28 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110">
+        <v>20107526</v>
+      </c>
+      <c r="B110" t="s">
+        <v>346</v>
+      </c>
+      <c r="C110" t="s">
         <v>102</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
         <v>12</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="E110" t="s">
         <v>131</v>
       </c>
-      <c r="D110" s="10">
-        <v>20107526</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F110" s="10" t="s">
+      <c r="F110" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="G110" s="11">
+      <c r="G110" s="8">
         <v>49.577461800000002</v>
       </c>
-      <c r="H110" s="11">
+      <c r="H110" s="8">
         <v>27.174936540000001</v>
       </c>
       <c r="I110">
@@ -6635,28 +6626,28 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111">
+        <v>20107590</v>
+      </c>
+      <c r="B111" t="s">
+        <v>346</v>
+      </c>
+      <c r="C111" t="s">
         <v>102</v>
       </c>
-      <c r="B111" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
         <v>132</v>
       </c>
-      <c r="D111" s="10">
-        <v>20107590</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F111" s="10" t="s">
+      <c r="F111" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="G111" s="11">
+      <c r="G111" s="8">
         <v>49.577325999999999</v>
       </c>
-      <c r="H111" s="11">
+      <c r="H111" s="8">
         <v>27.174803019999999</v>
       </c>
       <c r="I111">
@@ -6673,28 +6664,28 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112">
+        <v>20109023</v>
+      </c>
+      <c r="B112" t="s">
+        <v>232</v>
+      </c>
+      <c r="C112" t="s">
         <v>102</v>
       </c>
-      <c r="B112" t="s">
-        <v>19</v>
-      </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
         <v>133</v>
       </c>
-      <c r="D112" s="10">
-        <v>20109023</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F112" s="10" t="s">
+      <c r="F112" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G112" s="11">
+      <c r="G112" s="8">
         <v>49.57719024</v>
       </c>
-      <c r="H112" s="11">
+      <c r="H112" s="8">
         <v>27.17466945</v>
       </c>
       <c r="I112">
@@ -6711,28 +6702,28 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113">
+        <v>20138620</v>
+      </c>
+      <c r="B113" t="s">
+        <v>386</v>
+      </c>
+      <c r="C113" t="s">
         <v>102</v>
       </c>
-      <c r="B113" t="s">
-        <v>19</v>
-      </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" t="s">
         <v>134</v>
       </c>
-      <c r="D113" s="10">
-        <v>20138620</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="F113" s="10" t="s">
+      <c r="F113" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="8">
         <v>49.577054500000003</v>
       </c>
-      <c r="H113" s="11">
+      <c r="H113" s="8">
         <v>27.174535850000002</v>
       </c>
       <c r="I113">
@@ -6749,28 +6740,28 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114">
+        <v>20001212</v>
+      </c>
+      <c r="B114" t="s">
+        <v>388</v>
+      </c>
+      <c r="C114" t="s">
         <v>102</v>
       </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>12</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="E114" t="s">
         <v>135</v>
       </c>
-      <c r="D114" s="10">
-        <v>20001212</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="F114" s="10" t="s">
+      <c r="F114" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G114" s="11">
+      <c r="G114" s="8">
         <v>49.537453749999997</v>
       </c>
-      <c r="H114" s="11">
+      <c r="H114" s="8">
         <v>27.139537820000001</v>
       </c>
       <c r="I114">
@@ -6787,28 +6778,28 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115">
+        <v>20013524</v>
+      </c>
+      <c r="B115" t="s">
+        <v>390</v>
+      </c>
+      <c r="C115" t="s">
         <v>102</v>
       </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
         <v>12</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="E115" t="s">
         <v>136</v>
       </c>
-      <c r="D115" s="10">
-        <v>20013524</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="F115" s="10" t="s">
+      <c r="F115" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="G115" s="11">
+      <c r="G115" s="8">
         <v>49.537637709999998</v>
       </c>
-      <c r="H115" s="11">
+      <c r="H115" s="8">
         <v>27.139660169999999</v>
       </c>
       <c r="I115">
@@ -6825,28 +6816,28 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116">
+        <v>20046274</v>
+      </c>
+      <c r="B116" t="s">
+        <v>392</v>
+      </c>
+      <c r="C116" t="s">
         <v>102</v>
       </c>
-      <c r="B116" t="s">
+      <c r="D116" t="s">
         <v>12</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="E116" t="s">
         <v>137</v>
       </c>
-      <c r="D116" s="10">
-        <v>20046274</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="F116" s="10" t="s">
+      <c r="F116" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G116" s="11">
+      <c r="G116" s="8">
         <v>49.537852919999999</v>
       </c>
-      <c r="H116" s="11">
+      <c r="H116" s="8">
         <v>27.139804259999998</v>
       </c>
       <c r="I116">
@@ -6863,28 +6854,28 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117">
+        <v>20002303</v>
+      </c>
+      <c r="B117" t="s">
+        <v>394</v>
+      </c>
+      <c r="C117" t="s">
         <v>102</v>
       </c>
-      <c r="B117" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" t="s">
         <v>138</v>
       </c>
-      <c r="D117" s="10">
-        <v>20002303</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F117" s="10" t="s">
+      <c r="F117" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="G117" s="11">
+      <c r="G117" s="8">
         <v>49.538060590000001</v>
       </c>
-      <c r="H117" s="11">
+      <c r="H117" s="8">
         <v>27.13999768</v>
       </c>
       <c r="I117">
@@ -6901,28 +6892,28 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118">
+        <v>20062324</v>
+      </c>
+      <c r="B118" t="s">
+        <v>396</v>
+      </c>
+      <c r="C118" t="s">
         <v>102</v>
       </c>
-      <c r="B118" t="s">
-        <v>19</v>
-      </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" t="s">
         <v>139</v>
       </c>
-      <c r="D118" s="10">
-        <v>20062324</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="F118" s="10" t="s">
+      <c r="F118" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G118" s="11">
+      <c r="G118" s="8">
         <v>49.537880110000003</v>
       </c>
-      <c r="H118" s="11">
+      <c r="H118" s="8">
         <v>27.140215260000002</v>
       </c>
       <c r="I118">
@@ -6939,28 +6930,28 @@
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119">
+        <v>20025486</v>
+      </c>
+      <c r="B119" t="s">
+        <v>398</v>
+      </c>
+      <c r="C119" t="s">
         <v>102</v>
       </c>
-      <c r="B119" t="s">
-        <v>19</v>
-      </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" t="s">
         <v>140</v>
       </c>
-      <c r="D119" s="10">
-        <v>20025486</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F119" s="10" t="s">
+      <c r="F119" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="G119" s="11">
+      <c r="G119" s="8">
         <v>49.537760249999998</v>
       </c>
-      <c r="H119" s="11">
+      <c r="H119" s="8">
         <v>27.14036046</v>
       </c>
       <c r="I119">
@@ -6977,28 +6968,28 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120">
+        <v>20077010</v>
+      </c>
+      <c r="B120" t="s">
+        <v>400</v>
+      </c>
+      <c r="C120" t="s">
         <v>102</v>
       </c>
-      <c r="B120" t="s">
-        <v>19</v>
-      </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" t="s">
         <v>141</v>
       </c>
-      <c r="D120" s="10">
-        <v>20077010</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="F120" s="10" t="s">
+      <c r="F120" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="G120" s="11">
+      <c r="G120" s="8">
         <v>49.53764039</v>
       </c>
-      <c r="H120" s="11">
+      <c r="H120" s="8">
         <v>27.140505650000001</v>
       </c>
       <c r="I120">
@@ -7015,28 +7006,28 @@
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121">
+        <v>20078635</v>
+      </c>
+      <c r="B121" t="s">
+        <v>402</v>
+      </c>
+      <c r="C121" t="s">
         <v>102</v>
       </c>
-      <c r="B121" t="s">
+      <c r="D121" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="E121" t="s">
         <v>142</v>
       </c>
-      <c r="D121" s="10">
-        <v>20078635</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="F121" s="10" t="s">
+      <c r="F121" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="G121" s="11">
+      <c r="G121" s="8">
         <v>49.537520520000001</v>
       </c>
-      <c r="H121" s="11">
+      <c r="H121" s="8">
         <v>27.140650839999999</v>
       </c>
       <c r="I121">
@@ -7053,28 +7044,28 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122">
+        <v>20014255</v>
+      </c>
+      <c r="B122" t="s">
+        <v>404</v>
+      </c>
+      <c r="C122" t="s">
         <v>143</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
         <v>12</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="E122" t="s">
         <v>144</v>
       </c>
-      <c r="D122" s="10">
-        <v>20014255</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="F122" s="10" t="s">
+      <c r="F122" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="G122" s="11">
+      <c r="G122" s="8">
         <v>49.537243539999999</v>
       </c>
-      <c r="H122" s="11">
+      <c r="H122" s="8">
         <v>27.140986160000001</v>
       </c>
       <c r="I122">
@@ -7091,28 +7082,28 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123">
+        <v>20131568</v>
+      </c>
+      <c r="B123" t="s">
+        <v>406</v>
+      </c>
+      <c r="C123" t="s">
         <v>143</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
         <v>12</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="E123" t="s">
         <v>145</v>
       </c>
-      <c r="D123" s="10">
-        <v>20131568</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F123" s="10" t="s">
+      <c r="F123" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="G123" s="11">
+      <c r="G123" s="8">
         <v>49.537075309999999</v>
       </c>
-      <c r="H123" s="11">
+      <c r="H123" s="8">
         <v>27.141189740000002</v>
       </c>
       <c r="I123">
@@ -7129,28 +7120,28 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124">
+        <v>20110150</v>
+      </c>
+      <c r="B124" t="s">
+        <v>240</v>
+      </c>
+      <c r="C124" t="s">
         <v>143</v>
       </c>
-      <c r="B124" t="s">
+      <c r="D124" t="s">
         <v>12</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="E124" t="s">
         <v>146</v>
       </c>
-      <c r="D124" s="10">
-        <v>20110150</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F124" s="10" t="s">
+      <c r="F124" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G124" s="11">
+      <c r="G124" s="8">
         <v>49.53695956</v>
       </c>
-      <c r="H124" s="11">
+      <c r="H124" s="8">
         <v>27.141335170000001</v>
       </c>
       <c r="I124">
@@ -7167,28 +7158,28 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125">
+        <v>20077164</v>
+      </c>
+      <c r="B125" t="s">
+        <v>409</v>
+      </c>
+      <c r="C125" t="s">
         <v>143</v>
       </c>
-      <c r="B125" t="s">
+      <c r="D125" t="s">
         <v>12</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="E125" t="s">
         <v>147</v>
       </c>
-      <c r="D125" s="10">
-        <v>20077164</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F125" s="10" t="s">
+      <c r="F125" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="G125" s="11">
+      <c r="G125" s="8">
         <v>49.54627816</v>
       </c>
-      <c r="H125" s="11">
+      <c r="H125" s="8">
         <v>27.13376671</v>
       </c>
       <c r="I125">
@@ -7205,28 +7196,28 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126">
+        <v>20106948</v>
+      </c>
+      <c r="B126" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" t="s">
         <v>143</v>
       </c>
-      <c r="B126" t="s">
+      <c r="D126" t="s">
         <v>12</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="E126" t="s">
         <v>148</v>
       </c>
-      <c r="D126" s="10">
-        <v>20106948</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F126" s="10" t="s">
+      <c r="F126" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="G126" s="11">
+      <c r="G126" s="8">
         <v>49.546141390000003</v>
       </c>
-      <c r="H126" s="11">
+      <c r="H126" s="8">
         <v>27.13367336</v>
       </c>
       <c r="I126">
@@ -7243,28 +7234,28 @@
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127">
+        <v>20113090</v>
+      </c>
+      <c r="B127" t="s">
+        <v>189</v>
+      </c>
+      <c r="C127" t="s">
         <v>143</v>
       </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" t="s">
         <v>149</v>
       </c>
-      <c r="D127" s="10">
-        <v>20113090</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F127" s="10" t="s">
+      <c r="F127" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="G127" s="11">
+      <c r="G127" s="8">
         <v>49.546059790000001</v>
       </c>
-      <c r="H127" s="11">
+      <c r="H127" s="8">
         <v>27.13360428</v>
       </c>
       <c r="I127">
@@ -7281,28 +7272,28 @@
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128">
+        <v>20106947</v>
+      </c>
+      <c r="B128" t="s">
+        <v>250</v>
+      </c>
+      <c r="C128" t="s">
         <v>143</v>
       </c>
-      <c r="B128" t="s">
-        <v>19</v>
-      </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
         <v>150</v>
       </c>
-      <c r="D128" s="10">
-        <v>20106947</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F128" s="10" t="s">
+      <c r="F128" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="G128" s="11">
+      <c r="G128" s="8">
         <v>49.545980980000003</v>
       </c>
-      <c r="H128" s="11">
+      <c r="H128" s="8">
         <v>27.13353523</v>
       </c>
       <c r="I128">
@@ -7319,28 +7310,28 @@
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129">
+        <v>20122416</v>
+      </c>
+      <c r="B129" t="s">
+        <v>414</v>
+      </c>
+      <c r="C129" t="s">
         <v>143</v>
       </c>
-      <c r="B129" t="s">
-        <v>19</v>
-      </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
         <v>151</v>
       </c>
-      <c r="D129" s="10">
-        <v>20122416</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="F129" s="10" t="s">
+      <c r="F129" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="G129" s="11">
+      <c r="G129" s="8">
         <v>49.54590039</v>
       </c>
-      <c r="H129" s="11">
+      <c r="H129" s="8">
         <v>27.133466989999999</v>
       </c>
       <c r="I129">
@@ -7357,28 +7348,28 @@
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130">
+        <v>20088214</v>
+      </c>
+      <c r="B130" t="s">
+        <v>416</v>
+      </c>
+      <c r="C130" t="s">
         <v>143</v>
       </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
         <v>12</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="E130" t="s">
         <v>152</v>
       </c>
-      <c r="D130" s="10">
-        <v>20088214</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="F130" s="10" t="s">
+      <c r="F130" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="G130" s="11">
+      <c r="G130" s="8">
         <v>49.545819809999998</v>
       </c>
-      <c r="H130" s="11">
+      <c r="H130" s="8">
         <v>27.133398759999999</v>
       </c>
       <c r="I130">
@@ -7395,28 +7386,28 @@
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131">
+        <v>20069196</v>
+      </c>
+      <c r="B131" t="s">
+        <v>418</v>
+      </c>
+      <c r="C131" t="s">
         <v>143</v>
       </c>
-      <c r="B131" t="s">
-        <v>19</v>
-      </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" t="s">
         <v>153</v>
       </c>
-      <c r="D131" s="10">
-        <v>20069196</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="F131" s="10" t="s">
+      <c r="F131" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="G131" s="11">
+      <c r="G131" s="8">
         <v>49.545739230000002</v>
       </c>
-      <c r="H131" s="11">
+      <c r="H131" s="8">
         <v>27.13333051</v>
       </c>
       <c r="I131">
@@ -7433,28 +7424,28 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132">
+        <v>20123049</v>
+      </c>
+      <c r="B132" t="s">
+        <v>420</v>
+      </c>
+      <c r="C132" t="s">
         <v>143</v>
       </c>
-      <c r="B132" t="s">
-        <v>19</v>
-      </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" t="s">
         <v>154</v>
       </c>
-      <c r="D132" s="10">
-        <v>20123049</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="F132" s="10" t="s">
+      <c r="F132" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G132" s="11">
+      <c r="G132" s="8">
         <v>49.545657869999999</v>
       </c>
-      <c r="H132" s="11">
+      <c r="H132" s="8">
         <v>27.13326391</v>
       </c>
       <c r="I132">
@@ -7471,28 +7462,28 @@
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="A133">
+        <v>20105882</v>
+      </c>
+      <c r="B133" t="s">
+        <v>250</v>
+      </c>
+      <c r="C133" t="s">
         <v>143</v>
       </c>
-      <c r="B133" t="s">
-        <v>19</v>
-      </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" t="s">
         <v>155</v>
       </c>
-      <c r="D133" s="10">
-        <v>20105882</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F133" s="10" t="s">
+      <c r="F133" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="G133" s="11">
+      <c r="G133" s="8">
         <v>49.54557629</v>
       </c>
-      <c r="H133" s="11">
+      <c r="H133" s="8">
         <v>27.133194799999998</v>
       </c>
       <c r="I133">
@@ -7509,28 +7500,28 @@
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134">
+        <v>20112829</v>
+      </c>
+      <c r="B134" t="s">
+        <v>189</v>
+      </c>
+      <c r="C134" t="s">
         <v>143</v>
       </c>
-      <c r="B134" t="s">
-        <v>19</v>
-      </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" t="s">
         <v>156</v>
       </c>
-      <c r="D134" s="10">
-        <v>20112829</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F134" s="10" t="s">
+      <c r="F134" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="G134" s="11">
+      <c r="G134" s="8">
         <v>49.545497490000002</v>
       </c>
-      <c r="H134" s="11">
+      <c r="H134" s="8">
         <v>27.13312573</v>
       </c>
       <c r="I134">
@@ -7547,28 +7538,28 @@
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135">
+        <v>20074636</v>
+      </c>
+      <c r="B135" t="s">
+        <v>424</v>
+      </c>
+      <c r="C135" t="s">
         <v>143</v>
       </c>
-      <c r="B135" t="s">
+      <c r="D135" t="s">
         <v>12</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="E135" t="s">
         <v>157</v>
       </c>
-      <c r="D135" s="10">
-        <v>20074636</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="F135" s="10" t="s">
+      <c r="F135" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="G135" s="11">
+      <c r="G135" s="8">
         <v>49.545416930000002</v>
       </c>
-      <c r="H135" s="11">
+      <c r="H135" s="8">
         <v>27.1330575</v>
       </c>
       <c r="I135">
@@ -7585,28 +7576,28 @@
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136">
+        <v>20132843</v>
+      </c>
+      <c r="B136" t="s">
+        <v>426</v>
+      </c>
+      <c r="C136" t="s">
         <v>143</v>
       </c>
-      <c r="B136" t="s">
-        <v>19</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" t="s">
         <v>158</v>
       </c>
-      <c r="D136" s="10">
-        <v>20132843</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F136" s="10" t="s">
+      <c r="F136" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G136" s="11">
+      <c r="G136" s="8">
         <v>49.549935660000003</v>
       </c>
-      <c r="H136" s="11">
+      <c r="H136" s="8">
         <v>27.127975379999999</v>
       </c>
       <c r="I136">
@@ -7623,28 +7614,28 @@
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137">
+        <v>20046295</v>
+      </c>
+      <c r="B137" t="s">
+        <v>428</v>
+      </c>
+      <c r="C137" t="s">
         <v>143</v>
       </c>
-      <c r="B137" t="s">
-        <v>19</v>
-      </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" t="s">
         <v>159</v>
       </c>
-      <c r="D137" s="10">
-        <v>20046295</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="F137" s="10" t="s">
+      <c r="F137" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="G137" s="11">
+      <c r="G137" s="8">
         <v>49.549748350000002</v>
       </c>
-      <c r="H137" s="11">
+      <c r="H137" s="8">
         <v>27.127943429999998</v>
       </c>
       <c r="I137">
@@ -7661,28 +7652,28 @@
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138">
+        <v>20121645</v>
+      </c>
+      <c r="B138" t="s">
+        <v>430</v>
+      </c>
+      <c r="C138" t="s">
         <v>143</v>
       </c>
-      <c r="B138" t="s">
+      <c r="D138" t="s">
         <v>12</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="E138" t="s">
         <v>160</v>
       </c>
-      <c r="D138" s="10">
-        <v>20121645</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="F138" s="10" t="s">
+      <c r="F138" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="G138" s="11">
+      <c r="G138" s="8">
         <v>49.54955854</v>
       </c>
-      <c r="H138" s="11">
+      <c r="H138" s="8">
         <v>27.127909460000001</v>
       </c>
       <c r="I138">
@@ -7699,28 +7690,28 @@
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="A139">
+        <v>20080764</v>
+      </c>
+      <c r="B139" t="s">
+        <v>432</v>
+      </c>
+      <c r="C139" t="s">
         <v>143</v>
       </c>
-      <c r="B139" t="s">
-        <v>19</v>
-      </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" t="s">
         <v>161</v>
       </c>
-      <c r="D139" s="10">
-        <v>20080764</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="F139" s="10" t="s">
+      <c r="F139" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="G139" s="11">
+      <c r="G139" s="8">
         <v>49.549371890000003</v>
       </c>
-      <c r="H139" s="11">
+      <c r="H139" s="8">
         <v>27.12787441</v>
       </c>
       <c r="I139">
@@ -7737,28 +7728,28 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="A140">
+        <v>20084201</v>
+      </c>
+      <c r="B140" t="s">
+        <v>434</v>
+      </c>
+      <c r="C140" t="s">
         <v>143</v>
       </c>
-      <c r="B140" t="s">
-        <v>19</v>
-      </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" t="s">
         <v>162</v>
       </c>
-      <c r="D140" s="10">
-        <v>20084201</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="F140" s="10" t="s">
+      <c r="F140" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="G140" s="11">
+      <c r="G140" s="8">
         <v>49.549183970000001</v>
       </c>
-      <c r="H140" s="11">
+      <c r="H140" s="8">
         <v>27.127840719999998</v>
       </c>
       <c r="I140">
@@ -7775,28 +7766,28 @@
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141">
+        <v>20107474</v>
+      </c>
+      <c r="B141" t="s">
+        <v>346</v>
+      </c>
+      <c r="C141" t="s">
         <v>143</v>
       </c>
-      <c r="B141" t="s">
-        <v>19</v>
-      </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" t="s">
         <v>163</v>
       </c>
-      <c r="D141" s="10">
-        <v>20107474</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F141" s="10" t="s">
+      <c r="F141" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="G141" s="11">
+      <c r="G141" s="8">
         <v>49.548996099999997</v>
       </c>
-      <c r="H141" s="11">
+      <c r="H141" s="8">
         <v>27.127807050000001</v>
       </c>
       <c r="I141">
@@ -7813,28 +7804,28 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="A142">
+        <v>20061914</v>
+      </c>
+      <c r="B142" t="s">
+        <v>437</v>
+      </c>
+      <c r="C142" t="s">
         <v>143</v>
       </c>
-      <c r="B142" t="s">
-        <v>19</v>
-      </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" t="s">
         <v>164</v>
       </c>
-      <c r="D142" s="10">
-        <v>20061914</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F142" s="10" t="s">
+      <c r="F142" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="G142" s="11">
+      <c r="G142" s="8">
         <v>49.548808190000003</v>
       </c>
-      <c r="H142" s="11">
+      <c r="H142" s="8">
         <v>27.12777342</v>
       </c>
       <c r="I142">
@@ -7851,28 +7842,28 @@
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="A143">
+        <v>20062901</v>
+      </c>
+      <c r="B143" t="s">
+        <v>439</v>
+      </c>
+      <c r="C143" t="s">
         <v>143</v>
       </c>
-      <c r="B143" t="s">
-        <v>19</v>
-      </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" t="s">
         <v>165</v>
       </c>
-      <c r="D143" s="10">
-        <v>20062901</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="F143" s="10" t="s">
+      <c r="F143" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="G143" s="11">
+      <c r="G143" s="8">
         <v>49.54862026</v>
       </c>
-      <c r="H143" s="11">
+      <c r="H143" s="8">
         <v>27.127739739999999</v>
       </c>
       <c r="I143">
@@ -7889,28 +7880,28 @@
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="A144">
+        <v>20080850</v>
+      </c>
+      <c r="B144" t="s">
+        <v>441</v>
+      </c>
+      <c r="C144" t="s">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
-        <v>19</v>
-      </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" t="s">
         <v>166</v>
       </c>
-      <c r="D144" s="10">
-        <v>20080850</v>
-      </c>
-      <c r="E144" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="F144" s="10" t="s">
+      <c r="F144" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="G144" s="11">
+      <c r="G144" s="8">
         <v>49.548432949999999</v>
       </c>
-      <c r="H144" s="11">
+      <c r="H144" s="8">
         <v>27.1277078</v>
       </c>
       <c r="I144">
@@ -7927,28 +7918,28 @@
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="A145">
+        <v>20080798</v>
+      </c>
+      <c r="B145" t="s">
+        <v>443</v>
+      </c>
+      <c r="C145" t="s">
         <v>143</v>
       </c>
-      <c r="B145" t="s">
-        <v>19</v>
-      </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" t="s">
         <v>167</v>
       </c>
-      <c r="D145" s="10">
-        <v>20080798</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F145" s="10" t="s">
+      <c r="F145" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="G145" s="11">
+      <c r="G145" s="8">
         <v>49.548243139999997</v>
       </c>
-      <c r="H145" s="11">
+      <c r="H145" s="8">
         <v>27.1276738</v>
       </c>
       <c r="I145">
@@ -7965,28 +7956,28 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+      <c r="A146">
+        <v>20080860</v>
+      </c>
+      <c r="B146" t="s">
+        <v>445</v>
+      </c>
+      <c r="C146" t="s">
         <v>143</v>
       </c>
-      <c r="B146" t="s">
+      <c r="D146" t="s">
         <v>12</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="E146" t="s">
         <v>168</v>
       </c>
-      <c r="D146" s="10">
-        <v>20080860</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F146" s="10" t="s">
+      <c r="F146" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="G146" s="11">
+      <c r="G146" s="8">
         <v>49.548056330000001</v>
       </c>
-      <c r="H146" s="11">
+      <c r="H146" s="8">
         <v>27.127639800000001</v>
       </c>
       <c r="I146">
@@ -8003,28 +7994,28 @@
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+      <c r="A147">
+        <v>20015339</v>
+      </c>
+      <c r="B147" t="s">
+        <v>447</v>
+      </c>
+      <c r="C147" t="s">
         <v>143</v>
       </c>
-      <c r="B147" t="s">
+      <c r="D147" t="s">
         <v>12</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="E147" t="s">
         <v>169</v>
       </c>
-      <c r="D147" s="10">
-        <v>20015339</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="F147" s="10" t="s">
+      <c r="F147" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="G147" s="11">
+      <c r="G147" s="8">
         <v>49.524608049999998</v>
       </c>
-      <c r="H147" s="11">
+      <c r="H147" s="8">
         <v>27.135610799999998</v>
       </c>
       <c r="I147">
@@ -8041,28 +8032,28 @@
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="A148">
+        <v>20015212</v>
+      </c>
+      <c r="B148" t="s">
+        <v>449</v>
+      </c>
+      <c r="C148" t="s">
         <v>143</v>
       </c>
-      <c r="B148" t="s">
-        <v>19</v>
-      </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" t="s">
         <v>170</v>
       </c>
-      <c r="D148" s="10">
-        <v>20015212</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="F148" s="10" t="s">
+      <c r="F148" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="G148" s="11">
+      <c r="G148" s="8">
         <v>49.524771909999998</v>
       </c>
-      <c r="H148" s="11">
+      <c r="H148" s="8">
         <v>27.135714780000001</v>
       </c>
       <c r="I148">
@@ -8079,28 +8070,28 @@
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+      <c r="A149">
+        <v>20047021</v>
+      </c>
+      <c r="B149" t="s">
+        <v>451</v>
+      </c>
+      <c r="C149" t="s">
         <v>143</v>
       </c>
-      <c r="B149" t="s">
+      <c r="D149" t="s">
         <v>12</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="E149" t="s">
         <v>171</v>
       </c>
-      <c r="D149" s="10">
-        <v>20047021</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="F149" s="10" t="s">
+      <c r="F149" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="G149" s="11">
+      <c r="G149" s="8">
         <v>49.52501247</v>
       </c>
-      <c r="H149" s="11">
+      <c r="H149" s="8">
         <v>27.135832090000001</v>
       </c>
       <c r="I149">
@@ -8117,28 +8108,28 @@
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="A150">
+        <v>20087103</v>
+      </c>
+      <c r="B150" t="s">
+        <v>453</v>
+      </c>
+      <c r="C150" t="s">
         <v>143</v>
       </c>
-      <c r="B150" t="s">
+      <c r="D150" t="s">
         <v>12</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="E150" t="s">
         <v>172</v>
       </c>
-      <c r="D150" s="10">
-        <v>20087103</v>
-      </c>
-      <c r="E150" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="F150" s="10" t="s">
+      <c r="F150" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="G150" s="11">
+      <c r="G150" s="8">
         <v>49.525257779999997</v>
       </c>
-      <c r="H150" s="11">
+      <c r="H150" s="8">
         <v>27.135837590000001</v>
       </c>
       <c r="I150">
@@ -8155,28 +8146,28 @@
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="A151">
+        <v>20014976</v>
+      </c>
+      <c r="B151" t="s">
+        <v>455</v>
+      </c>
+      <c r="C151" t="s">
         <v>143</v>
       </c>
-      <c r="B151" t="s">
-        <v>19</v>
-      </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="s">
         <v>173</v>
       </c>
-      <c r="D151" s="10">
-        <v>20014976</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="F151" s="10" t="s">
+      <c r="F151" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="G151" s="11">
+      <c r="G151" s="8">
         <v>49.525661210000003</v>
       </c>
-      <c r="H151" s="11">
+      <c r="H151" s="8">
         <v>27.135797400000001</v>
       </c>
       <c r="I151">
@@ -8193,28 +8184,28 @@
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="A152">
+        <v>20013659</v>
+      </c>
+      <c r="B152" t="s">
+        <v>457</v>
+      </c>
+      <c r="C152" t="s">
         <v>143</v>
       </c>
-      <c r="B152" t="s">
+      <c r="D152" t="s">
         <v>12</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="E152" t="s">
         <v>174</v>
       </c>
-      <c r="D152" s="10">
-        <v>20013659</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="F152" s="10" t="s">
+      <c r="F152" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="G152" s="11">
+      <c r="G152" s="8">
         <v>49.525858970000002</v>
       </c>
-      <c r="H152" s="11">
+      <c r="H152" s="8">
         <v>27.13575689</v>
       </c>
       <c r="I152">
@@ -8231,28 +8222,28 @@
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+      <c r="A153">
+        <v>20015737</v>
+      </c>
+      <c r="B153" t="s">
+        <v>459</v>
+      </c>
+      <c r="C153" t="s">
         <v>143</v>
       </c>
-      <c r="B153" t="s">
-        <v>19</v>
-      </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" t="s">
         <v>175</v>
       </c>
-      <c r="D153" s="10">
-        <v>20015737</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F153" s="10" t="s">
+      <c r="F153" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="G153" s="11">
+      <c r="G153" s="8">
         <v>49.526095349999999</v>
       </c>
-      <c r="H153" s="11">
+      <c r="H153" s="8">
         <v>27.13568562</v>
       </c>
       <c r="I153">
@@ -8269,28 +8260,28 @@
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+      <c r="A154">
+        <v>20015738</v>
+      </c>
+      <c r="B154" t="s">
+        <v>459</v>
+      </c>
+      <c r="C154" t="s">
         <v>143</v>
       </c>
-      <c r="B154" t="s">
-        <v>19</v>
-      </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" t="s">
         <v>176</v>
       </c>
-      <c r="D154" s="10">
-        <v>20015738</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F154" s="10" t="s">
+      <c r="F154" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="G154" s="11">
+      <c r="G154" s="8">
         <v>49.526290250000002</v>
       </c>
-      <c r="H154" s="11">
+      <c r="H154" s="8">
         <v>27.135505869999999</v>
       </c>
       <c r="I154">
@@ -8307,28 +8298,28 @@
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="A155">
+        <v>20027202</v>
+      </c>
+      <c r="B155" t="s">
+        <v>462</v>
+      </c>
+      <c r="C155" t="s">
         <v>143</v>
       </c>
-      <c r="B155" t="s">
-        <v>19</v>
-      </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" t="s">
         <v>177</v>
       </c>
-      <c r="D155" s="10">
-        <v>20027202</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="F155" s="10" t="s">
+      <c r="F155" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="G155" s="11">
+      <c r="G155" s="8">
         <v>49.526542360000001</v>
       </c>
-      <c r="H155" s="11">
+      <c r="H155" s="8">
         <v>27.13522201</v>
       </c>
       <c r="I155">
@@ -8345,28 +8336,28 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156">
+        <v>20115380</v>
+      </c>
+      <c r="B156" t="s">
+        <v>232</v>
+      </c>
+      <c r="C156" t="s">
         <v>143</v>
       </c>
-      <c r="B156" t="s">
-        <v>19</v>
-      </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="s">
         <v>178</v>
       </c>
-      <c r="D156" s="10">
-        <v>20115380</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F156" s="10" t="s">
+      <c r="F156" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="G156" s="11">
+      <c r="G156" s="8">
         <v>49.526707539999997</v>
       </c>
-      <c r="H156" s="11">
+      <c r="H156" s="8">
         <v>27.135022899999999</v>
       </c>
       <c r="I156">
@@ -8383,28 +8374,28 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="A157">
+        <v>20088002</v>
+      </c>
+      <c r="B157" t="s">
+        <v>465</v>
+      </c>
+      <c r="C157" t="s">
         <v>143</v>
       </c>
-      <c r="B157" t="s">
-        <v>19</v>
-      </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" t="s">
         <v>179</v>
       </c>
-      <c r="D157" s="10">
-        <v>20088002</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="F157" s="10" t="s">
+      <c r="F157" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="G157" s="11">
+      <c r="G157" s="8">
         <v>49.52635085</v>
       </c>
-      <c r="H157" s="11">
+      <c r="H157" s="8">
         <v>27.13470835</v>
       </c>
       <c r="I157">
@@ -8421,28 +8412,28 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="A158">
+        <v>20089638</v>
+      </c>
+      <c r="B158" t="s">
+        <v>467</v>
+      </c>
+      <c r="C158" t="s">
         <v>143</v>
       </c>
-      <c r="B158" t="s">
+      <c r="D158" t="s">
         <v>12</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="E158" t="s">
         <v>180</v>
       </c>
-      <c r="D158" s="10">
-        <v>20089638</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="F158" s="10" t="s">
+      <c r="F158" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="G158" s="11">
+      <c r="G158" s="8">
         <v>49.539208739999999</v>
       </c>
-      <c r="H158" s="11">
+      <c r="H158" s="8">
         <v>27.11741666</v>
       </c>
       <c r="I158">
@@ -8459,28 +8450,28 @@
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="A159">
+        <v>20122943</v>
+      </c>
+      <c r="B159" t="s">
+        <v>469</v>
+      </c>
+      <c r="C159" t="s">
         <v>143</v>
       </c>
-      <c r="B159" t="s">
+      <c r="D159" t="s">
         <v>12</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="E159" t="s">
         <v>181</v>
       </c>
-      <c r="D159" s="10">
-        <v>20122943</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F159" s="10" t="s">
+      <c r="F159" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="G159" s="11">
+      <c r="G159" s="8">
         <v>49.53923897</v>
       </c>
-      <c r="H159" s="11">
+      <c r="H159" s="8">
         <v>27.117597790000001</v>
       </c>
       <c r="I159">
@@ -8497,28 +8488,28 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="A160">
+        <v>20014378</v>
+      </c>
+      <c r="B160" t="s">
+        <v>471</v>
+      </c>
+      <c r="C160" t="s">
         <v>143</v>
       </c>
-      <c r="B160" t="s">
-        <v>19</v>
-      </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" t="s">
+        <v>19</v>
+      </c>
+      <c r="E160" t="s">
         <v>182</v>
       </c>
-      <c r="D160" s="10">
-        <v>20014378</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="F160" s="10" t="s">
+      <c r="F160" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="G160" s="11">
+      <c r="G160" s="8">
         <v>49.539266840000003</v>
       </c>
-      <c r="H160" s="11">
+      <c r="H160" s="8">
         <v>27.117775259999998</v>
       </c>
       <c r="I160">
@@ -8535,28 +8526,28 @@
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+      <c r="A161">
+        <v>20065543</v>
+      </c>
+      <c r="B161" t="s">
+        <v>473</v>
+      </c>
+      <c r="C161" t="s">
         <v>143</v>
       </c>
-      <c r="B161" t="s">
+      <c r="D161" t="s">
         <v>12</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="E161" t="s">
         <v>183</v>
       </c>
-      <c r="D161" s="10">
-        <v>20065543</v>
-      </c>
-      <c r="E161" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="F161" s="10" t="s">
+      <c r="F161" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="G161" s="11">
+      <c r="G161" s="8">
         <v>49.539300619999999</v>
       </c>
-      <c r="H161" s="11">
+      <c r="H161" s="8">
         <v>27.117975990000001</v>
       </c>
       <c r="I161">
@@ -8573,28 +8564,28 @@
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+      <c r="A162">
+        <v>20107761</v>
+      </c>
+      <c r="B162" t="s">
+        <v>475</v>
+      </c>
+      <c r="C162" t="s">
         <v>11</v>
       </c>
-      <c r="B162" t="s">
+      <c r="D162" t="s">
         <v>12</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="E162" t="s">
         <v>13</v>
       </c>
-      <c r="D162" s="10">
-        <v>20107761</v>
-      </c>
-      <c r="E162" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="F162" s="10" t="s">
+      <c r="F162" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="G162" s="11">
+      <c r="G162" s="8">
         <v>49.539060249999999</v>
       </c>
-      <c r="H162" s="11">
+      <c r="H162" s="8">
         <v>27.118151869999998</v>
       </c>
       <c r="I162">
@@ -8611,28 +8602,28 @@
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+      <c r="A163">
+        <v>20076528</v>
+      </c>
+      <c r="B163" t="s">
+        <v>477</v>
+      </c>
+      <c r="C163" t="s">
         <v>11</v>
       </c>
-      <c r="B163" t="s">
+      <c r="D163" t="s">
         <v>12</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="E163" t="s">
         <v>16</v>
       </c>
-      <c r="D163" s="10">
-        <v>20076528</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="F163" s="10" t="s">
+      <c r="F163" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="G163" s="11">
+      <c r="G163" s="8">
         <v>49.53884979</v>
       </c>
-      <c r="H163" s="11">
+      <c r="H163" s="8">
         <v>27.118174629999999</v>
       </c>
       <c r="I163">
@@ -8649,28 +8640,28 @@
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+      <c r="A164">
+        <v>20072560</v>
+      </c>
+      <c r="B164" t="s">
+        <v>479</v>
+      </c>
+      <c r="C164" t="s">
         <v>11</v>
       </c>
-      <c r="B164" t="s">
-        <v>19</v>
-      </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" t="s">
+        <v>19</v>
+      </c>
+      <c r="E164" t="s">
         <v>20</v>
       </c>
-      <c r="D164" s="10">
-        <v>20072560</v>
-      </c>
-      <c r="E164" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="F164" s="10" t="s">
+      <c r="F164" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="G164" s="11">
+      <c r="G164" s="8">
         <v>49.538624540000001</v>
       </c>
-      <c r="H164" s="11">
+      <c r="H164" s="8">
         <v>27.11819882</v>
       </c>
       <c r="I164">
@@ -8687,28 +8678,28 @@
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+      <c r="A165">
+        <v>20015490</v>
+      </c>
+      <c r="B165" t="s">
+        <v>481</v>
+      </c>
+      <c r="C165" t="s">
         <v>11</v>
       </c>
-      <c r="B165" t="s">
+      <c r="D165" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="E165" t="s">
         <v>22</v>
       </c>
-      <c r="D165" s="10">
-        <v>20015490</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="F165" s="10" t="s">
+      <c r="F165" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="G165" s="11">
+      <c r="G165" s="8">
         <v>49.538398899999997</v>
       </c>
-      <c r="H165" s="11">
+      <c r="H165" s="8">
         <v>27.118223390000001</v>
       </c>
       <c r="I165">
@@ -8725,28 +8716,28 @@
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="A166">
+        <v>20101935</v>
+      </c>
+      <c r="B166" t="s">
+        <v>483</v>
+      </c>
+      <c r="C166" t="s">
         <v>11</v>
       </c>
-      <c r="B166" t="s">
-        <v>19</v>
-      </c>
-      <c r="C166" s="1" t="s">
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="s">
         <v>23</v>
       </c>
-      <c r="D166" s="10">
-        <v>20101935</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="F166" s="10" t="s">
+      <c r="F166" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G166" s="11">
+      <c r="G166" s="8">
         <v>49.538198800000004</v>
       </c>
-      <c r="H166" s="11">
+      <c r="H166" s="8">
         <v>27.118245040000001</v>
       </c>
       <c r="I166">
@@ -8763,28 +8754,28 @@
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+      <c r="A167">
+        <v>20067652</v>
+      </c>
+      <c r="B167" t="s">
+        <v>485</v>
+      </c>
+      <c r="C167" t="s">
         <v>11</v>
       </c>
-      <c r="B167" t="s">
-        <v>19</v>
-      </c>
-      <c r="C167" s="1" t="s">
+      <c r="D167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" t="s">
         <v>25</v>
       </c>
-      <c r="D167" s="10">
-        <v>20067652</v>
-      </c>
-      <c r="E167" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="F167" s="10" t="s">
+      <c r="F167" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="G167" s="11">
+      <c r="G167" s="8">
         <v>49.537998219999999</v>
       </c>
-      <c r="H167" s="11">
+      <c r="H167" s="8">
         <v>27.118266569999999</v>
       </c>
       <c r="I167">
@@ -8801,28 +8792,28 @@
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+      <c r="A168">
+        <v>20107427</v>
+      </c>
+      <c r="B168" t="s">
+        <v>250</v>
+      </c>
+      <c r="C168" t="s">
         <v>11</v>
       </c>
-      <c r="B168" t="s">
+      <c r="D168" t="s">
         <v>12</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="E168" t="s">
         <v>26</v>
       </c>
-      <c r="D168" s="10">
-        <v>20107427</v>
-      </c>
-      <c r="E168" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F168" s="10" t="s">
+      <c r="F168" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="G168" s="11">
+      <c r="G168" s="8">
         <v>49.537778150000001</v>
       </c>
-      <c r="H168" s="11">
+      <c r="H168" s="8">
         <v>27.118290399999999</v>
       </c>
       <c r="I168">
@@ -8839,28 +8830,28 @@
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="A169">
+        <v>20187427</v>
+      </c>
+      <c r="B169" t="s">
+        <v>488</v>
+      </c>
+      <c r="C169" t="s">
         <v>11</v>
       </c>
-      <c r="B169" t="s">
-        <v>19</v>
-      </c>
-      <c r="C169" s="1" t="s">
+      <c r="D169" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" t="s">
         <v>27</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E169" s="1" t="s">
+      <c r="F169" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="F169" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="G169" s="11">
+      <c r="G169" s="8">
         <v>49.516048439999999</v>
       </c>
-      <c r="H169" s="11">
+      <c r="H169" s="8">
         <v>27.103339340000002</v>
       </c>
       <c r="I169">
@@ -8877,28 +8868,28 @@
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+      <c r="A170">
+        <v>20146509</v>
+      </c>
+      <c r="B170" t="s">
+        <v>490</v>
+      </c>
+      <c r="C170" t="s">
         <v>11</v>
       </c>
-      <c r="B170" t="s">
-        <v>19</v>
-      </c>
-      <c r="C170" s="1" t="s">
+      <c r="D170" t="s">
+        <v>19</v>
+      </c>
+      <c r="E170" t="s">
         <v>28</v>
       </c>
-      <c r="D170" s="1">
-        <v>20146509</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="F170" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="F170" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="G170" s="11">
+      <c r="G170" s="8">
         <v>49.516208669999997</v>
       </c>
-      <c r="H170" s="11">
+      <c r="H170" s="8">
         <v>27.103432130000002</v>
       </c>
       <c r="I170">
@@ -8915,28 +8906,28 @@
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+      <c r="A171">
+        <v>20146860</v>
+      </c>
+      <c r="B171" t="s">
+        <v>492</v>
+      </c>
+      <c r="C171" t="s">
         <v>11</v>
       </c>
-      <c r="B171" t="s">
-        <v>19</v>
-      </c>
-      <c r="C171" s="1" t="s">
+      <c r="D171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="s">
         <v>29</v>
       </c>
-      <c r="D171" s="1">
-        <v>20146860</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="F171" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="F171" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="G171" s="11">
+      <c r="G171" s="8">
         <v>49.516368919999998</v>
       </c>
-      <c r="H171" s="11">
+      <c r="H171" s="8">
         <v>27.103526129999999</v>
       </c>
       <c r="I171">
@@ -8953,28 +8944,28 @@
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+      <c r="A172">
+        <v>20142540</v>
+      </c>
+      <c r="B172" t="s">
+        <v>494</v>
+      </c>
+      <c r="C172" t="s">
         <v>11</v>
       </c>
-      <c r="B172" t="s">
-        <v>19</v>
-      </c>
-      <c r="C172" s="1" t="s">
+      <c r="D172" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" t="s">
         <v>30</v>
       </c>
-      <c r="D172" s="1">
-        <v>20142540</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="F172" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F172" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="G172" s="11">
+      <c r="G172" s="8">
         <v>49.516527920000001</v>
       </c>
-      <c r="H172" s="11">
+      <c r="H172" s="8">
         <v>27.103620589999998</v>
       </c>
       <c r="I172">
@@ -8991,28 +8982,28 @@
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+      <c r="A173">
+        <v>20146859</v>
+      </c>
+      <c r="B173" t="s">
+        <v>496</v>
+      </c>
+      <c r="C173" t="s">
         <v>11</v>
       </c>
-      <c r="B173" t="s">
+      <c r="D173" t="s">
         <v>12</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="E173" t="s">
         <v>31</v>
       </c>
-      <c r="D173" s="1">
-        <v>20146859</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="F173" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F173" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="G173" s="11">
+      <c r="G173" s="8">
         <v>49.516706720000002</v>
       </c>
-      <c r="H173" s="11">
+      <c r="H173" s="8">
         <v>27.10377282</v>
       </c>
       <c r="I173">
@@ -9029,28 +9020,28 @@
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+      <c r="A174">
+        <v>20146858</v>
+      </c>
+      <c r="B174" t="s">
+        <v>498</v>
+      </c>
+      <c r="C174" t="s">
         <v>11</v>
       </c>
-      <c r="B174" t="s">
+      <c r="D174" t="s">
         <v>12</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="E174" t="s">
         <v>32</v>
       </c>
-      <c r="D174" s="1">
-        <v>20146858</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="F174" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F174" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="G174" s="11">
+      <c r="G174" s="8">
         <v>49.516866970000002</v>
       </c>
-      <c r="H174" s="11">
+      <c r="H174" s="8">
         <v>27.10386682</v>
       </c>
       <c r="I174">
@@ -9067,28 +9058,28 @@
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+      <c r="A175">
+        <v>20146857</v>
+      </c>
+      <c r="B175" t="s">
+        <v>500</v>
+      </c>
+      <c r="C175" t="s">
         <v>11</v>
       </c>
-      <c r="B175" t="s">
+      <c r="D175" t="s">
         <v>12</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="E175" t="s">
         <v>33</v>
       </c>
-      <c r="D175" s="1">
-        <v>20146857</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="F175" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="F175" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="G175" s="11">
+      <c r="G175" s="8">
         <v>49.517027220000003</v>
       </c>
-      <c r="H175" s="11">
+      <c r="H175" s="8">
         <v>27.103960820000001</v>
       </c>
       <c r="I175">
@@ -9105,28 +9096,28 @@
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="A176">
+        <v>20146856</v>
+      </c>
+      <c r="B176" t="s">
+        <v>502</v>
+      </c>
+      <c r="C176" t="s">
         <v>11</v>
       </c>
-      <c r="B176" t="s">
+      <c r="D176" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="E176" t="s">
         <v>34</v>
       </c>
-      <c r="D176" s="1">
-        <v>20146856</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="F176" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="F176" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="G176" s="11">
+      <c r="G176" s="8">
         <v>49.517187470000003</v>
       </c>
-      <c r="H176" s="11">
+      <c r="H176" s="8">
         <v>27.104054810000001</v>
       </c>
       <c r="I176">
@@ -9143,28 +9134,28 @@
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+      <c r="A177">
+        <v>20146855</v>
+      </c>
+      <c r="B177" t="s">
+        <v>504</v>
+      </c>
+      <c r="C177" t="s">
         <v>11</v>
       </c>
-      <c r="B177" t="s">
-        <v>19</v>
-      </c>
-      <c r="C177" s="1" t="s">
+      <c r="D177" t="s">
+        <v>19</v>
+      </c>
+      <c r="E177" t="s">
         <v>35</v>
       </c>
-      <c r="D177" s="1">
-        <v>20146855</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="F177" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F177" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="G177" s="11">
+      <c r="G177" s="8">
         <v>49.517389889999997</v>
       </c>
-      <c r="H177" s="11">
+      <c r="H177" s="8">
         <v>27.104173549999999</v>
       </c>
       <c r="I177">
@@ -9181,28 +9172,28 @@
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+      <c r="A178">
+        <v>20146854</v>
+      </c>
+      <c r="B178" t="s">
+        <v>506</v>
+      </c>
+      <c r="C178" t="s">
         <v>11</v>
       </c>
-      <c r="B178" t="s">
-        <v>19</v>
-      </c>
-      <c r="C178" s="1" t="s">
+      <c r="D178" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" t="s">
         <v>36</v>
       </c>
-      <c r="D178" s="1">
-        <v>20146854</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="F178" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F178" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="G178" s="11">
+      <c r="G178" s="8">
         <v>49.517549090000003</v>
       </c>
-      <c r="H178" s="11">
+      <c r="H178" s="8">
         <v>27.10426794</v>
       </c>
       <c r="I178">
@@ -9219,28 +9210,28 @@
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
+      <c r="A179">
+        <v>20141512</v>
+      </c>
+      <c r="B179" t="s">
+        <v>508</v>
+      </c>
+      <c r="C179" t="s">
         <v>11</v>
       </c>
-      <c r="B179" t="s">
+      <c r="D179" t="s">
         <v>12</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="E179" t="s">
         <v>37</v>
       </c>
-      <c r="D179" s="1">
-        <v>20141512</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="F179" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="F179" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="G179" s="11">
+      <c r="G179" s="8">
         <v>49.517737140000001</v>
       </c>
-      <c r="H179" s="11">
+      <c r="H179" s="8">
         <v>27.104361149999999</v>
       </c>
       <c r="I179">
@@ -9257,28 +9248,28 @@
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
+      <c r="A180">
+        <v>20161695</v>
+      </c>
+      <c r="B180" t="s">
+        <v>510</v>
+      </c>
+      <c r="C180" t="s">
         <v>11</v>
       </c>
-      <c r="B180" t="s">
-        <v>19</v>
-      </c>
-      <c r="C180" s="1" t="s">
+      <c r="D180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" t="s">
         <v>38</v>
       </c>
-      <c r="D180" s="1">
-        <v>20161695</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="F180" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F180" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="G180" s="11">
+      <c r="G180" s="8">
         <v>49.504515720000001</v>
       </c>
-      <c r="H180" s="11">
+      <c r="H180" s="8">
         <v>27.087462219999999</v>
       </c>
       <c r="I180">
@@ -9295,28 +9286,28 @@
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
+      <c r="A181">
+        <v>20161696</v>
+      </c>
+      <c r="B181" t="s">
+        <v>512</v>
+      </c>
+      <c r="C181" t="s">
         <v>11</v>
       </c>
-      <c r="B181" t="s">
-        <v>19</v>
-      </c>
-      <c r="C181" s="1" t="s">
+      <c r="D181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="s">
         <v>39</v>
       </c>
-      <c r="D181" s="1">
-        <v>20161696</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="F181" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="F181" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="G181" s="11">
+      <c r="G181" s="8">
         <v>49.504660049999998</v>
       </c>
-      <c r="H181" s="11">
+      <c r="H181" s="8">
         <v>27.087356450000001</v>
       </c>
       <c r="I181">
@@ -9333,28 +9324,28 @@
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
+      <c r="A182">
+        <v>20161697</v>
+      </c>
+      <c r="B182" t="s">
+        <v>514</v>
+      </c>
+      <c r="C182" t="s">
         <v>11</v>
       </c>
-      <c r="B182" t="s">
-        <v>19</v>
-      </c>
-      <c r="C182" s="1" t="s">
+      <c r="D182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="s">
         <v>40</v>
       </c>
-      <c r="D182" s="1">
-        <v>20161697</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="F182" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="F182" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="G182" s="11">
+      <c r="G182" s="8">
         <v>49.504804370000002</v>
       </c>
-      <c r="H182" s="11">
+      <c r="H182" s="8">
         <v>27.08725067</v>
       </c>
       <c r="I182">
@@ -9371,28 +9362,28 @@
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
+      <c r="A183">
+        <v>20161698</v>
+      </c>
+      <c r="B183" t="s">
+        <v>516</v>
+      </c>
+      <c r="C183" t="s">
         <v>11</v>
       </c>
-      <c r="B183" t="s">
+      <c r="D183" t="s">
         <v>12</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="E183" t="s">
         <v>41</v>
       </c>
-      <c r="D183" s="1">
-        <v>20161698</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="F183" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F183" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="G183" s="11">
+      <c r="G183" s="8">
         <v>49.5049487</v>
       </c>
-      <c r="H183" s="11">
+      <c r="H183" s="8">
         <v>27.087144890000001</v>
       </c>
       <c r="I183">
@@ -9409,28 +9400,28 @@
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+      <c r="A184">
+        <v>20161699</v>
+      </c>
+      <c r="B184" t="s">
+        <v>518</v>
+      </c>
+      <c r="C184" t="s">
         <v>11</v>
       </c>
-      <c r="B184" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="1" t="s">
+      <c r="D184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" t="s">
         <v>42</v>
       </c>
-      <c r="D184" s="1">
-        <v>20161699</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="F184" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F184" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="G184" s="11">
+      <c r="G184" s="8">
         <v>49.50509692</v>
       </c>
-      <c r="H184" s="11">
+      <c r="H184" s="8">
         <v>27.087036260000001</v>
       </c>
       <c r="I184">
@@ -9447,28 +9438,28 @@
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
+      <c r="A185">
+        <v>20161700</v>
+      </c>
+      <c r="B185" t="s">
+        <v>520</v>
+      </c>
+      <c r="C185" t="s">
         <v>11</v>
       </c>
-      <c r="B185" t="s">
+      <c r="D185" t="s">
         <v>12</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="E185" t="s">
         <v>43</v>
       </c>
-      <c r="D185" s="1">
-        <v>20161700</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="F185" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="F185" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="G185" s="11">
+      <c r="G185" s="8">
         <v>49.506086170000003</v>
       </c>
-      <c r="H185" s="11">
+      <c r="H185" s="8">
         <v>27.087569340000002</v>
       </c>
       <c r="I185">
@@ -9485,28 +9476,28 @@
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+      <c r="A186">
+        <v>20161701</v>
+      </c>
+      <c r="B186" t="s">
+        <v>522</v>
+      </c>
+      <c r="C186" t="s">
         <v>11</v>
       </c>
-      <c r="B186" t="s">
+      <c r="D186" t="s">
         <v>12</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="E186" t="s">
         <v>45</v>
       </c>
-      <c r="D186" s="1">
-        <v>20161701</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="F186" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F186" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="G186" s="11">
+      <c r="G186" s="8">
         <v>49.505965789999998</v>
       </c>
-      <c r="H186" s="11">
+      <c r="H186" s="8">
         <v>27.08743759</v>
       </c>
       <c r="I186">
@@ -9523,28 +9514,28 @@
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
+      <c r="A187">
+        <v>20161702</v>
+      </c>
+      <c r="B187" t="s">
+        <v>524</v>
+      </c>
+      <c r="C187" t="s">
         <v>11</v>
       </c>
-      <c r="B187" t="s">
+      <c r="D187" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="E187" t="s">
         <v>46</v>
       </c>
-      <c r="D187" s="1">
-        <v>20161702</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="F187" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="F187" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="G187" s="11">
+      <c r="G187" s="8">
         <v>49.505847609999996</v>
       </c>
-      <c r="H187" s="11">
+      <c r="H187" s="8">
         <v>27.087308409999999</v>
       </c>
       <c r="I187">
@@ -9561,28 +9552,28 @@
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
+      <c r="A188">
+        <v>20161703</v>
+      </c>
+      <c r="B188" t="s">
+        <v>526</v>
+      </c>
+      <c r="C188" t="s">
         <v>11</v>
       </c>
-      <c r="B188" t="s">
+      <c r="D188" t="s">
         <v>12</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="E188" t="s">
         <v>47</v>
       </c>
-      <c r="D188" s="1">
-        <v>20161703</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="F188" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="F188" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="G188" s="11">
+      <c r="G188" s="8">
         <v>49.505729440000003</v>
       </c>
-      <c r="H188" s="11">
+      <c r="H188" s="8">
         <v>27.08717923</v>
       </c>
       <c r="I188">
@@ -9599,28 +9590,28 @@
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
+      <c r="A189">
+        <v>20161704</v>
+      </c>
+      <c r="B189" t="s">
+        <v>528</v>
+      </c>
+      <c r="C189" t="s">
         <v>11</v>
       </c>
-      <c r="B189" t="s">
-        <v>19</v>
-      </c>
-      <c r="C189" s="1" t="s">
+      <c r="D189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" t="s">
         <v>48</v>
       </c>
-      <c r="D189" s="1">
-        <v>20161704</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="F189" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="F189" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="G189" s="11">
+      <c r="G189" s="8">
         <v>49.505611260000002</v>
       </c>
-      <c r="H189" s="11">
+      <c r="H189" s="8">
         <v>27.087050049999998</v>
       </c>
       <c r="I189">
@@ -9637,28 +9628,28 @@
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
+      <c r="A190">
+        <v>20161705</v>
+      </c>
+      <c r="B190" t="s">
+        <v>530</v>
+      </c>
+      <c r="C190" t="s">
         <v>11</v>
       </c>
-      <c r="B190" t="s">
-        <v>19</v>
-      </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="s">
         <v>49</v>
       </c>
-      <c r="D190" s="1">
-        <v>20161705</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="F190" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F190" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="G190" s="11">
+      <c r="G190" s="8">
         <v>49.505493080000001</v>
       </c>
-      <c r="H190" s="11">
+      <c r="H190" s="8">
         <v>27.08692087</v>
       </c>
       <c r="I190">
@@ -9675,28 +9666,28 @@
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
+      <c r="A191">
+        <v>20170756</v>
+      </c>
+      <c r="B191" t="s">
+        <v>291</v>
+      </c>
+      <c r="C191" t="s">
         <v>11</v>
       </c>
-      <c r="B191" t="s">
-        <v>19</v>
-      </c>
-      <c r="C191" s="1" t="s">
+      <c r="D191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="s">
         <v>50</v>
       </c>
-      <c r="D191" s="1">
-        <v>20170756</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="G191" s="11">
+      <c r="F191" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="G191" s="8">
         <v>49.56054563</v>
       </c>
-      <c r="H191" s="11">
+      <c r="H191" s="8">
         <v>27.111372880000001</v>
       </c>
       <c r="I191">
@@ -9713,28 +9704,28 @@
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
+      <c r="A192">
+        <v>20176048</v>
+      </c>
+      <c r="B192" t="s">
+        <v>291</v>
+      </c>
+      <c r="C192" t="s">
         <v>11</v>
       </c>
-      <c r="B192" t="s">
-        <v>19</v>
-      </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="s">
         <v>51</v>
       </c>
-      <c r="D192" s="1">
-        <v>20176048</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="G192" s="11">
+      <c r="F192" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G192" s="8">
         <v>49.560502249999999</v>
       </c>
-      <c r="H192" s="11">
+      <c r="H192" s="8">
         <v>27.111374179999999</v>
       </c>
       <c r="I192">
@@ -9751,28 +9742,28 @@
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
+      <c r="A193">
+        <v>20159842</v>
+      </c>
+      <c r="B193" t="s">
+        <v>291</v>
+      </c>
+      <c r="C193" t="s">
         <v>11</v>
       </c>
-      <c r="B193" t="s">
+      <c r="D193" t="s">
         <v>12</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="E193" t="s">
         <v>52</v>
       </c>
-      <c r="D193" s="1">
-        <v>20159842</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F193" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="G193" s="11">
+      <c r="F193" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G193" s="8">
         <v>49.560471620000001</v>
       </c>
-      <c r="H193" s="11">
+      <c r="H193" s="8">
         <v>27.111402909999999</v>
       </c>
       <c r="I193">
@@ -9789,28 +9780,28 @@
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+      <c r="A194">
+        <v>50168907</v>
+      </c>
+      <c r="B194" t="s">
+        <v>291</v>
+      </c>
+      <c r="C194" t="s">
         <v>11</v>
       </c>
-      <c r="B194" t="s">
-        <v>19</v>
-      </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="s">
         <v>53</v>
       </c>
-      <c r="D194" s="1">
-        <v>50168907</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="G194" s="11">
+      <c r="F194" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="G194" s="8">
         <v>49.560518960000003</v>
       </c>
-      <c r="H194" s="11">
+      <c r="H194" s="8">
         <v>27.111403809999999</v>
       </c>
       <c r="I194">
@@ -9827,28 +9818,28 @@
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
+      <c r="A195">
+        <v>20160472</v>
+      </c>
+      <c r="B195" t="s">
+        <v>291</v>
+      </c>
+      <c r="C195" t="s">
         <v>11</v>
       </c>
-      <c r="B195" t="s">
+      <c r="D195" t="s">
         <v>12</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="E195" t="s">
         <v>54</v>
       </c>
-      <c r="D195" s="1">
-        <v>20160472</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>537</v>
-      </c>
-      <c r="G195" s="11">
+      <c r="F195" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="G195" s="8">
         <v>49.560504129999998</v>
       </c>
-      <c r="H195" s="11">
+      <c r="H195" s="8">
         <v>27.111430720000001</v>
       </c>
       <c r="I195">
@@ -9865,28 +9856,28 @@
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
+      <c r="A196">
+        <v>20160439</v>
+      </c>
+      <c r="B196" t="s">
+        <v>291</v>
+      </c>
+      <c r="C196" t="s">
         <v>11</v>
       </c>
-      <c r="B196" t="s">
-        <v>19</v>
-      </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="s">
         <v>55</v>
       </c>
-      <c r="D196" s="1">
-        <v>20160439</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="G196" s="11">
+      <c r="F196" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="G196" s="8">
         <v>49.560491210000002</v>
       </c>
-      <c r="H196" s="11">
+      <c r="H196" s="8">
         <v>27.111393060000001</v>
       </c>
       <c r="I196">
@@ -9903,28 +9894,28 @@
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
+      <c r="A197">
+        <v>20160471</v>
+      </c>
+      <c r="B197" t="s">
+        <v>291</v>
+      </c>
+      <c r="C197" t="s">
         <v>11</v>
       </c>
-      <c r="B197" t="s">
+      <c r="D197" t="s">
         <v>12</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="E197" t="s">
         <v>56</v>
       </c>
-      <c r="D197" s="1">
-        <v>20160471</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F197" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="G197" s="11">
+      <c r="F197" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="G197" s="8">
         <v>49.560424329999996</v>
       </c>
-      <c r="H197" s="11">
+      <c r="H197" s="8">
         <v>27.11136183</v>
       </c>
       <c r="I197">
@@ -9941,28 +9932,28 @@
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
+      <c r="A198">
+        <v>20160470</v>
+      </c>
+      <c r="B198" t="s">
+        <v>291</v>
+      </c>
+      <c r="C198" t="s">
         <v>11</v>
       </c>
-      <c r="B198" t="s">
-        <v>19</v>
-      </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="s">
         <v>57</v>
       </c>
-      <c r="D198" s="1">
-        <v>20160470</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="G198" s="11">
+      <c r="F198" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G198" s="8">
         <v>49.560492439999997</v>
       </c>
-      <c r="H198" s="11">
+      <c r="H198" s="8">
         <v>27.111431549999999</v>
       </c>
       <c r="I198">
@@ -9979,28 +9970,28 @@
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
+      <c r="A199">
+        <v>20160469</v>
+      </c>
+      <c r="B199" t="s">
+        <v>291</v>
+      </c>
+      <c r="C199" t="s">
         <v>11</v>
       </c>
-      <c r="B199" t="s">
-        <v>19</v>
-      </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="s">
         <v>58</v>
       </c>
-      <c r="D199" s="1">
-        <v>20160469</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="G199" s="11">
+      <c r="F199" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="G199" s="8">
         <v>49.56067754</v>
       </c>
-      <c r="H199" s="11">
+      <c r="H199" s="8">
         <v>27.11109506</v>
       </c>
       <c r="I199">
@@ -10017,28 +10008,28 @@
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
+      <c r="A200">
+        <v>20160465</v>
+      </c>
+      <c r="B200" t="s">
+        <v>291</v>
+      </c>
+      <c r="C200" t="s">
         <v>11</v>
       </c>
-      <c r="B200" t="s">
-        <v>19</v>
-      </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" t="s">
+        <v>19</v>
+      </c>
+      <c r="E200" t="s">
         <v>59</v>
       </c>
-      <c r="D200" s="1">
-        <v>20160465</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>542</v>
-      </c>
-      <c r="G200" s="11">
+      <c r="F200" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="G200" s="8">
         <v>49.560652529999999</v>
       </c>
-      <c r="H200" s="11">
+      <c r="H200" s="8">
         <v>27.111069279999999</v>
       </c>
       <c r="I200">
@@ -10055,28 +10046,28 @@
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
+      <c r="A201">
+        <v>20176525</v>
+      </c>
+      <c r="B201" t="s">
+        <v>291</v>
+      </c>
+      <c r="C201" t="s">
         <v>11</v>
       </c>
-      <c r="B201" t="s">
+      <c r="D201" t="s">
         <v>12</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="E201" t="s">
         <v>60</v>
       </c>
-      <c r="D201" s="1">
-        <v>20176525</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="G201" s="11">
+      <c r="F201" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="G201" s="8">
         <v>49.560661109999998</v>
       </c>
-      <c r="H201" s="11">
+      <c r="H201" s="8">
         <v>27.11107303</v>
       </c>
       <c r="I201">
@@ -10093,28 +10084,28 @@
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
+      <c r="A202">
+        <v>20161199</v>
+      </c>
+      <c r="B202" t="s">
+        <v>291</v>
+      </c>
+      <c r="C202" t="s">
         <v>61</v>
       </c>
-      <c r="B202" t="s">
-        <v>19</v>
-      </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" t="s">
         <v>62</v>
       </c>
-      <c r="D202" s="10">
-        <v>20161199</v>
-      </c>
-      <c r="E202" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="G202" s="11">
+      <c r="F202" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="G202" s="8">
         <v>49.56449035</v>
       </c>
-      <c r="H202" s="11">
+      <c r="H202" s="8">
         <v>27.105736839999999</v>
       </c>
       <c r="I202">
@@ -10131,28 +10122,28 @@
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
+      <c r="A203">
+        <v>20161200</v>
+      </c>
+      <c r="B203" t="s">
+        <v>291</v>
+      </c>
+      <c r="C203" t="s">
         <v>61</v>
       </c>
-      <c r="B203" t="s">
+      <c r="D203" t="s">
         <v>12</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="E203" t="s">
         <v>63</v>
       </c>
-      <c r="D203" s="10">
-        <v>20161200</v>
-      </c>
-      <c r="E203" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="G203" s="11">
+      <c r="F203" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="G203" s="8">
         <v>49.569020180000003</v>
       </c>
-      <c r="H203" s="11">
+      <c r="H203" s="8">
         <v>27.10803658</v>
       </c>
       <c r="I203">
@@ -10169,28 +10160,28 @@
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
+      <c r="A204">
+        <v>20161198</v>
+      </c>
+      <c r="B204" t="s">
+        <v>291</v>
+      </c>
+      <c r="C204" t="s">
         <v>61</v>
       </c>
-      <c r="B204" t="s">
-        <v>19</v>
-      </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" t="s">
         <v>64</v>
       </c>
-      <c r="D204" s="10">
-        <v>20161198</v>
-      </c>
-      <c r="E204" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F204" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="G204" s="11">
+      <c r="F204" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="G204" s="8">
         <v>49.563253279999998</v>
       </c>
-      <c r="H204" s="11">
+      <c r="H204" s="8">
         <v>27.10562908</v>
       </c>
       <c r="I204">
@@ -10207,28 +10198,28 @@
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
+      <c r="A205">
+        <v>20168003</v>
+      </c>
+      <c r="B205" t="s">
+        <v>559</v>
+      </c>
+      <c r="C205" t="s">
         <v>61</v>
       </c>
-      <c r="B205" t="s">
+      <c r="D205" t="s">
         <v>12</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="E205" t="s">
         <v>65</v>
       </c>
-      <c r="D205" s="1">
-        <v>20168003</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F205" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="G205" s="11">
+      <c r="F205" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="G205" s="8">
         <v>49.510560150000003</v>
       </c>
-      <c r="H205" s="11">
+      <c r="H205" s="8">
         <v>27.103797650000001</v>
       </c>
       <c r="I205">
@@ -10245,28 +10236,28 @@
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
+      <c r="A206">
+        <v>20168002</v>
+      </c>
+      <c r="B206" t="s">
+        <v>559</v>
+      </c>
+      <c r="C206" t="s">
         <v>61</v>
       </c>
-      <c r="B206" t="s">
-        <v>19</v>
-      </c>
-      <c r="C206" s="1" t="s">
+      <c r="D206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206" t="s">
         <v>66</v>
       </c>
-      <c r="D206" s="1">
-        <v>20168002</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F206" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="G206" s="11">
+      <c r="F206" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="G206" s="8">
         <v>49.509839960000001</v>
       </c>
-      <c r="H206" s="11">
+      <c r="H206" s="8">
         <v>27.10356633</v>
       </c>
       <c r="I206">
@@ -10283,28 +10274,28 @@
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
+      <c r="A207">
+        <v>20168001</v>
+      </c>
+      <c r="B207" t="s">
+        <v>559</v>
+      </c>
+      <c r="C207" t="s">
         <v>61</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207" t="s">
         <v>12</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="E207" t="s">
         <v>67</v>
       </c>
-      <c r="D207" s="1">
-        <v>20168001</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F207" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="G207" s="11">
+      <c r="F207" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G207" s="8">
         <v>49.509998529999997</v>
       </c>
-      <c r="H207" s="11">
+      <c r="H207" s="8">
         <v>27.10373963</v>
       </c>
       <c r="I207">
@@ -10321,28 +10312,28 @@
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
+      <c r="A208">
+        <v>20168000</v>
+      </c>
+      <c r="B208" t="s">
+        <v>559</v>
+      </c>
+      <c r="C208" t="s">
         <v>61</v>
       </c>
-      <c r="B208" t="s">
+      <c r="D208" t="s">
         <v>12</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="E208" t="s">
         <v>68</v>
       </c>
-      <c r="D208" s="1">
-        <v>20168000</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F208" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="G208" s="11">
+      <c r="F208" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G208" s="8">
         <v>49.509660580000002</v>
       </c>
-      <c r="H208" s="11">
+      <c r="H208" s="8">
         <v>27.10369674</v>
       </c>
       <c r="I208">
@@ -10359,28 +10350,28 @@
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
+      <c r="A209">
+        <v>20167999</v>
+      </c>
+      <c r="B209" t="s">
+        <v>559</v>
+      </c>
+      <c r="C209" t="s">
         <v>61</v>
       </c>
-      <c r="B209" t="s">
+      <c r="D209" t="s">
         <v>12</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="E209" t="s">
         <v>69</v>
       </c>
-      <c r="D209" s="1">
-        <v>20167999</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="G209" s="11">
+      <c r="F209" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G209" s="8">
         <v>49.509820310000002</v>
       </c>
-      <c r="H209" s="11">
+      <c r="H209" s="8">
         <v>27.103871300000002</v>
       </c>
       <c r="I209">
@@ -10397,28 +10388,28 @@
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
+      <c r="A210">
+        <v>20167998</v>
+      </c>
+      <c r="B210" t="s">
+        <v>559</v>
+      </c>
+      <c r="C210" t="s">
         <v>61</v>
       </c>
-      <c r="B210" t="s">
-        <v>19</v>
-      </c>
-      <c r="C210" s="1" t="s">
+      <c r="D210" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" t="s">
         <v>70</v>
       </c>
-      <c r="D210" s="1">
-        <v>20167998</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="G210" s="11">
+      <c r="F210" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G210" s="8">
         <v>49.509482349999999</v>
       </c>
-      <c r="H210" s="11">
+      <c r="H210" s="8">
         <v>27.103828409999998</v>
       </c>
       <c r="I210">
@@ -10435,28 +10426,28 @@
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+      <c r="A211">
+        <v>20167997</v>
+      </c>
+      <c r="B211" t="s">
+        <v>559</v>
+      </c>
+      <c r="C211" t="s">
         <v>61</v>
       </c>
-      <c r="B211" t="s">
+      <c r="D211" t="s">
         <v>12</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="E211" t="s">
         <v>86</v>
       </c>
-      <c r="D211" s="1">
-        <v>20167997</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="G211" s="11">
+      <c r="F211" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G211" s="8">
         <v>49.509640920000002</v>
       </c>
-      <c r="H211" s="11">
+      <c r="H211" s="8">
         <v>27.104001700000001</v>
       </c>
       <c r="I211">
@@ -10473,28 +10464,28 @@
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
+      <c r="A212">
+        <v>20167996</v>
+      </c>
+      <c r="B212" t="s">
+        <v>559</v>
+      </c>
+      <c r="C212" t="s">
         <v>61</v>
       </c>
-      <c r="B212" t="s">
+      <c r="D212" t="s">
         <v>12</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="E212" t="s">
         <v>87</v>
       </c>
-      <c r="D212" s="1">
-        <v>20167996</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="G212" s="11">
+      <c r="F212" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="G212" s="8">
         <v>49.509168879999997</v>
       </c>
-      <c r="H212" s="11">
+      <c r="H212" s="8">
         <v>27.10405798</v>
       </c>
       <c r="I212">
@@ -10511,28 +10502,28 @@
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
+      <c r="A213">
+        <v>20167995</v>
+      </c>
+      <c r="B213" t="s">
+        <v>559</v>
+      </c>
+      <c r="C213" t="s">
         <v>61</v>
       </c>
-      <c r="B213" t="s">
+      <c r="D213" t="s">
         <v>12</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="E213" t="s">
         <v>88</v>
       </c>
-      <c r="D213" s="1">
-        <v>20167995</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="G213" s="11">
+      <c r="F213" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G213" s="8">
         <v>49.509327759999998</v>
       </c>
-      <c r="H213" s="11">
+      <c r="H213" s="8">
         <v>27.10423055</v>
       </c>
       <c r="I213">
@@ -10549,28 +10540,28 @@
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
+      <c r="A214">
+        <v>20167922</v>
+      </c>
+      <c r="B214" t="s">
+        <v>559</v>
+      </c>
+      <c r="C214" t="s">
         <v>61</v>
       </c>
-      <c r="B214" t="s">
+      <c r="D214" t="s">
         <v>12</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="E214" t="s">
         <v>89</v>
       </c>
-      <c r="D214" s="1">
-        <v>20167922</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F214" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="G214" s="11">
+      <c r="F214" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="G214" s="8">
         <v>49.509618099999997</v>
       </c>
-      <c r="H214" s="11">
+      <c r="H214" s="8">
         <v>27.105763060000001</v>
       </c>
       <c r="I214">
@@ -10587,28 +10578,28 @@
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
+      <c r="A215">
+        <v>20167994</v>
+      </c>
+      <c r="B215" t="s">
+        <v>559</v>
+      </c>
+      <c r="C215" t="s">
         <v>61</v>
       </c>
-      <c r="B215" t="s">
+      <c r="D215" t="s">
         <v>12</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="E215" t="s">
         <v>90</v>
       </c>
-      <c r="D215" s="1">
-        <v>20167994</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="G215" s="11">
+      <c r="F215" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G215" s="8">
         <v>49.508958380000003</v>
       </c>
-      <c r="H215" s="11">
+      <c r="H215" s="8">
         <v>27.10421135</v>
       </c>
       <c r="I215">
@@ -10625,28 +10616,28 @@
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
+      <c r="A216">
+        <v>20174421</v>
+      </c>
+      <c r="B216" t="s">
+        <v>559</v>
+      </c>
+      <c r="C216" t="s">
         <v>11</v>
       </c>
-      <c r="B216" t="s">
+      <c r="D216" t="s">
         <v>12</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="E216" t="s">
         <v>13</v>
       </c>
-      <c r="D216" s="1">
-        <v>20174421</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="G216" s="11">
+      <c r="F216" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G216" s="8">
         <v>49.509117089999997</v>
       </c>
-      <c r="H216" s="11">
+      <c r="H216" s="8">
         <v>27.10438585</v>
       </c>
       <c r="I216">
@@ -10663,28 +10654,28 @@
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
+      <c r="A217">
+        <v>20167992</v>
+      </c>
+      <c r="B217" t="s">
+        <v>559</v>
+      </c>
+      <c r="C217" t="s">
         <v>11</v>
       </c>
-      <c r="B217" t="s">
+      <c r="D217" t="s">
         <v>12</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="E217" t="s">
         <v>16</v>
       </c>
-      <c r="D217" s="1">
-        <v>20167992</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="G217" s="11">
+      <c r="F217" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="G217" s="8">
         <v>49.508693110000003</v>
       </c>
-      <c r="H217" s="11">
+      <c r="H217" s="8">
         <v>27.104405750000002</v>
       </c>
       <c r="I217">
@@ -10701,125 +10692,85 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="A2:A12">
+    <cfRule type="duplicateValues" dxfId="42" priority="42"/>
     <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D23">
+  <conditionalFormatting sqref="A13:A23">
+    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
     <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D23">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D24:D34">
+  <conditionalFormatting sqref="A24:A34">
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
     <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D24:D34">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D35:D45">
+  <conditionalFormatting sqref="A35:A45">
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
     <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D35:D45">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D46:D56">
+  <conditionalFormatting sqref="A46:A56">
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
     <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D46:D56">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D57:D69">
+  <conditionalFormatting sqref="A57:A69">
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
     <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D57:D69">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D70:D80">
+  <conditionalFormatting sqref="A70:A80">
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
     <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D70:D80">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D81:D91">
+  <conditionalFormatting sqref="A81:A91">
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
     <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D81:D91">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D92:D102">
+  <conditionalFormatting sqref="A92:A102">
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
     <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D92:D102">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+  <conditionalFormatting sqref="A103:A113">
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D103:D113">
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D103:D113">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D114:D124">
+  <conditionalFormatting sqref="A114:A124">
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
     <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D114:D124">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D125:D135">
+  <conditionalFormatting sqref="A125:A135">
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
     <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D125:D135">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D136:D146">
+  <conditionalFormatting sqref="A136:A146">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
     <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D136:D146">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D147:D157">
+  <conditionalFormatting sqref="A147:A157">
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
     <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D147:D157">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D158:D168">
+  <conditionalFormatting sqref="A158:A169">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
     <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D158:D168">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D169:D179">
+  <conditionalFormatting sqref="A170:A179">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
     <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D169:D179">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D180:D190">
+  <conditionalFormatting sqref="A180:A190">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
     <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D180:D190">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D191:D201">
+  <conditionalFormatting sqref="A191:A201">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
     <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D191:D201">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  <conditionalFormatting sqref="A202:A204">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D202:D204">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D202:D204">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D205:D217">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D205:D217">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A205:A217">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
